--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13159,10 +13159,10 @@
         <v>46276</v>
       </c>
       <c r="B1164" t="n">
-        <v>126.1999969482422</v>
+        <v>125.120002746582</v>
       </c>
       <c r="C1164" t="n">
-        <v>223.5299987792969</v>
+        <v>216.7200012207031</v>
       </c>
     </row>
   </sheetData>
@@ -13201,10 +13201,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.8796754235521398</v>
+        <v>-1.727927233361137</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1433591934970391</v>
+        <v>-2.907578198984417</v>
       </c>
     </row>
     <row r="3">
@@ -13862,10 +13862,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>8.821243097230202</v>
+        <v>7.889972777067999</v>
       </c>
       <c r="C2" t="n">
-        <v>5.032417576587189</v>
+        <v>1.832531605237175</v>
       </c>
     </row>
     <row r="3">
@@ -23865,10 +23865,10 @@
         <v>46276</v>
       </c>
       <c r="B889" t="n">
-        <v>38.42272620690799</v>
+        <v>37.23813234560414</v>
       </c>
       <c r="C889" t="n">
-        <v>85.9805260327454</v>
+        <v>80.31449939137505</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1164"/>
+  <dimension ref="A1:C1165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13163,6 +13163,17 @@
       </c>
       <c r="C1164" t="n">
         <v>216.7200012207031</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1165" t="n">
+        <v>123.620002746582</v>
+      </c>
+      <c r="C1165" t="n">
+        <v>214.6699981689453</v>
       </c>
     </row>
   </sheetData>
@@ -13201,10 +13212,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.727927233361137</v>
+        <v>-2.906061072188804</v>
       </c>
       <c r="C2" t="n">
-        <v>-2.907578198984417</v>
+        <v>-3.825997172191886</v>
       </c>
     </row>
     <row r="3">
@@ -13862,10 +13873,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>7.889972777067999</v>
+        <v>6.596534832590151</v>
       </c>
       <c r="C2" t="n">
-        <v>1.832531605237175</v>
+        <v>0.8692748712804121</v>
       </c>
     </row>
     <row r="3">
@@ -14083,7 +14094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C889"/>
+  <dimension ref="A1:C890"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23869,6 +23880,17 @@
       </c>
       <c r="C889" t="n">
         <v>80.31449939137505</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B890" t="n">
+        <v>35.99560029862909</v>
+      </c>
+      <c r="C890" t="n">
+        <v>79.88101621952812</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1165"/>
+  <dimension ref="A1:C1166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13167,12 +13167,23 @@
     </row>
     <row r="1165">
       <c r="A1165" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1165" t="n">
+        <v>125.120002746582</v>
+      </c>
+      <c r="C1165" t="n">
+        <v>216.7200012207031</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="2" t="n">
         <v>46280</v>
       </c>
-      <c r="B1165" t="n">
+      <c r="B1166" t="n">
         <v>123.620002746582</v>
       </c>
-      <c r="C1165" t="n">
+      <c r="C1166" t="n">
         <v>214.6699981689453</v>
       </c>
     </row>
@@ -14094,7 +14105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C890"/>
+  <dimension ref="A1:C891"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23884,13 +23895,24 @@
     </row>
     <row r="890">
       <c r="A890" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B890" t="n">
+        <v>37.64576528743051</v>
+      </c>
+      <c r="C890" t="n">
+        <v>81.59879995898258</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="2" t="n">
         <v>46280</v>
       </c>
-      <c r="B890" t="n">
-        <v>35.99560029862909</v>
-      </c>
-      <c r="C890" t="n">
-        <v>79.88101621952812</v>
+      <c r="B891" t="n">
+        <v>36.41580114744003</v>
+      </c>
+      <c r="C891" t="n">
+        <v>79.94131825446109</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13178,13 +13178,13 @@
     </row>
     <row r="1166">
       <c r="A1166" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B1166" t="n">
-        <v>123.620002746582</v>
+        <v>124.9100036621094</v>
       </c>
       <c r="C1166" t="n">
-        <v>214.6699981689453</v>
+        <v>218.4600067138672</v>
       </c>
     </row>
   </sheetData>
@@ -13223,10 +13223,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-2.906061072188804</v>
+        <v>-1.892865251721187</v>
       </c>
       <c r="C2" t="n">
-        <v>-3.825997172191886</v>
+        <v>-2.128040794375774</v>
       </c>
     </row>
     <row r="3">
@@ -13884,10 +13884,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>6.596534832590151</v>
+        <v>7.708892254292965</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8692748712804121</v>
+        <v>2.65012648977887</v>
       </c>
     </row>
     <row r="3">
@@ -23906,13 +23906,13 @@
     </row>
     <row r="891">
       <c r="A891" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B891" t="n">
-        <v>36.41580114744003</v>
+        <v>37.83932892986</v>
       </c>
       <c r="C891" t="n">
-        <v>79.94131825446109</v>
+        <v>83.11819038184703</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1166"/>
+  <dimension ref="A1:C1167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13178,13 +13178,24 @@
     </row>
     <row r="1166">
       <c r="A1166" s="2" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B1166" t="n">
-        <v>124.9100036621094</v>
+        <v>123.620002746582</v>
       </c>
       <c r="C1166" t="n">
-        <v>218.4600067138672</v>
+        <v>214.6699981689453</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1167" t="n">
+        <v>124.4300003051758</v>
+      </c>
+      <c r="C1167" t="n">
+        <v>216.6399993896484</v>
       </c>
     </row>
   </sheetData>
@@ -13223,10 +13234,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.892865251721187</v>
+        <v>-2.269870716757405</v>
       </c>
       <c r="C2" t="n">
-        <v>-2.128040794375774</v>
+        <v>-2.943419706375816</v>
       </c>
     </row>
     <row r="3">
@@ -13884,10 +13895,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>7.708892254292965</v>
+        <v>7.294989217403214</v>
       </c>
       <c r="C2" t="n">
-        <v>2.65012648977887</v>
+        <v>1.794940294128522</v>
       </c>
     </row>
     <row r="3">
@@ -14105,7 +14116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C891"/>
+  <dimension ref="A1:C892"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23906,13 +23917,24 @@
     </row>
     <row r="891">
       <c r="A891" s="2" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B891" t="n">
-        <v>37.83932892986</v>
+        <v>36.41580114744003</v>
       </c>
       <c r="C891" t="n">
-        <v>83.11819038184703</v>
+        <v>79.94131825446109</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B892" t="n">
+        <v>36.34669887409168</v>
+      </c>
+      <c r="C892" t="n">
+        <v>75.19003151706119</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1167"/>
+  <dimension ref="A1:C1168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13189,13 +13189,24 @@
     </row>
     <row r="1167">
       <c r="A1167" s="2" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B1167" t="n">
-        <v>124.4300003051758</v>
+        <v>124.9100036621094</v>
       </c>
       <c r="C1167" t="n">
-        <v>216.6399993896484</v>
+        <v>218.4600067138672</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1168" t="n">
+        <v>126.4100036621094</v>
+      </c>
+      <c r="C1168" t="n">
+        <v>224.2899932861328</v>
       </c>
     </row>
   </sheetData>
@@ -13234,10 +13245,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-2.269870716757405</v>
+        <v>-0.7147314128935212</v>
       </c>
       <c r="C2" t="n">
-        <v>-2.943419706375816</v>
+        <v>0.483843259612482</v>
       </c>
     </row>
     <row r="3">
@@ -13895,10 +13906,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>7.294989217403214</v>
+        <v>9.002330198770814</v>
       </c>
       <c r="C2" t="n">
-        <v>1.794940294128522</v>
+        <v>5.389524277405089</v>
       </c>
     </row>
     <row r="3">
@@ -14116,7 +14127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C892"/>
+  <dimension ref="A1:C893"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23928,13 +23939,24 @@
     </row>
     <row r="892">
       <c r="A892" s="2" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B892" t="n">
-        <v>36.34669887409168</v>
+        <v>36.8726722969468</v>
       </c>
       <c r="C892" t="n">
-        <v>75.19003151706119</v>
+        <v>76.66181485065364</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B893" t="n">
+        <v>39.03432270996905</v>
+      </c>
+      <c r="C893" t="n">
+        <v>82.23106105734679</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13203,10 +13203,10 @@
         <v>46283</v>
       </c>
       <c r="B1168" t="n">
-        <v>126.4100036621094</v>
+        <v>126.4800033569336</v>
       </c>
       <c r="C1168" t="n">
-        <v>224.2899932861328</v>
+        <v>224.0700073242188</v>
       </c>
     </row>
   </sheetData>
@@ -13245,10 +13245,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.7147314128935212</v>
+        <v>-0.6597520734401785</v>
       </c>
       <c r="C2" t="n">
-        <v>0.483843259612482</v>
+        <v>0.3852876593718246</v>
       </c>
     </row>
     <row r="3">
@@ -13906,10 +13906,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>9.002330198770814</v>
+        <v>9.062690373029159</v>
       </c>
       <c r="C2" t="n">
-        <v>5.389524277405089</v>
+        <v>5.286157134118175</v>
       </c>
     </row>
     <row r="3">
@@ -23953,10 +23953,10 @@
         <v>46283</v>
       </c>
       <c r="B893" t="n">
-        <v>39.03432270996905</v>
+        <v>39.11131313697516</v>
       </c>
       <c r="C893" t="n">
-        <v>82.23106105734679</v>
+        <v>82.05232693430378</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1168"/>
+  <dimension ref="A1:C1169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13200,13 +13200,24 @@
     </row>
     <row r="1168">
       <c r="A1168" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1168" t="n">
+        <v>124.4300003051758</v>
+      </c>
+      <c r="C1168" t="n">
+        <v>216.6399993896484</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="2" t="n">
         <v>46283</v>
       </c>
-      <c r="B1168" t="n">
-        <v>126.4800033569336</v>
-      </c>
-      <c r="C1168" t="n">
-        <v>224.0700073242188</v>
+      <c r="B1169" t="n">
+        <v>124.4300003051758</v>
+      </c>
+      <c r="C1169" t="n">
+        <v>216.6399993896484</v>
       </c>
     </row>
   </sheetData>
@@ -13245,10 +13256,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.6597520734401785</v>
+        <v>-2.269870716757405</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3852876593718246</v>
+        <v>-2.943419706375816</v>
       </c>
     </row>
     <row r="3">
@@ -13906,10 +13917,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>9.062690373029159</v>
+        <v>7.294989217403214</v>
       </c>
       <c r="C2" t="n">
-        <v>5.286157134118175</v>
+        <v>1.794940294128522</v>
       </c>
     </row>
     <row r="3">
@@ -14127,7 +14138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C893"/>
+  <dimension ref="A1:C894"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23950,13 +23961,24 @@
     </row>
     <row r="893">
       <c r="A893" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B893" t="n">
+        <v>36.85658030256776</v>
+      </c>
+      <c r="C893" t="n">
+        <v>76.01559649553673</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="2" t="n">
         <v>46283</v>
       </c>
-      <c r="B893" t="n">
-        <v>39.11131313697516</v>
-      </c>
-      <c r="C893" t="n">
-        <v>82.05232693430378</v>
+      <c r="B894" t="n">
+        <v>34.85423738175244</v>
+      </c>
+      <c r="C894" t="n">
+        <v>73.8404707229797</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13214,10 +13214,10 @@
         <v>46283</v>
       </c>
       <c r="B1169" t="n">
-        <v>124.4300003051758</v>
+        <v>126.4800033569336</v>
       </c>
       <c r="C1169" t="n">
-        <v>216.6399993896484</v>
+        <v>224.0700073242188</v>
       </c>
     </row>
   </sheetData>
@@ -13256,10 +13256,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-2.269870716757405</v>
+        <v>-0.6597520734401785</v>
       </c>
       <c r="C2" t="n">
-        <v>-2.943419706375816</v>
+        <v>0.3852876593718246</v>
       </c>
     </row>
     <row r="3">
@@ -13917,10 +13917,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>7.294989217403214</v>
+        <v>9.062690373029159</v>
       </c>
       <c r="C2" t="n">
-        <v>1.794940294128522</v>
+        <v>5.286157134118175</v>
       </c>
     </row>
     <row r="3">
@@ -23975,10 +23975,10 @@
         <v>46283</v>
       </c>
       <c r="B894" t="n">
-        <v>34.85423738175244</v>
+        <v>37.07598131406012</v>
       </c>
       <c r="C894" t="n">
-        <v>73.8404707229797</v>
+        <v>79.80260181816146</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1169"/>
+  <dimension ref="A1:C1170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13218,6 +13218,17 @@
       </c>
       <c r="C1169" t="n">
         <v>224.0700073242188</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1170" t="n">
+        <v>125.620002746582</v>
+      </c>
+      <c r="C1170" t="n">
+        <v>222.3000030517578</v>
       </c>
     </row>
   </sheetData>
@@ -13256,10 +13267,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.6597520734401785</v>
+        <v>-1.335215953751923</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3852876593718246</v>
+        <v>-0.4076894560000155</v>
       </c>
     </row>
     <row r="3">
@@ -13917,10 +13928,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>9.062690373029159</v>
+        <v>8.321118758560608</v>
       </c>
       <c r="C2" t="n">
-        <v>5.286157134118175</v>
+        <v>4.454466404136914</v>
       </c>
     </row>
     <row r="3">
@@ -14138,7 +14149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C894"/>
+  <dimension ref="A1:C895"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23979,6 +23990,17 @@
       </c>
       <c r="C894" t="n">
         <v>79.80260181816146</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B895" t="n">
+        <v>37.66575643461045</v>
+      </c>
+      <c r="C895" t="n">
+        <v>82.57227262778687</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13225,10 +13225,10 @@
         <v>46286</v>
       </c>
       <c r="B1170" t="n">
-        <v>125.620002746582</v>
+        <v>125.5699996948242</v>
       </c>
       <c r="C1170" t="n">
-        <v>222.3000030517578</v>
+        <v>222.2100067138672</v>
       </c>
     </row>
   </sheetData>
@@ -13267,10 +13267,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.335215953751923</v>
+        <v>-1.374489478632268</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4076894560000155</v>
+        <v>-0.448008588289639</v>
       </c>
     </row>
     <row r="3">
@@ -13928,10 +13928,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>8.321118758560608</v>
+        <v>8.278001528905122</v>
       </c>
       <c r="C2" t="n">
-        <v>4.454466404136914</v>
+        <v>4.412178867818262</v>
       </c>
     </row>
     <row r="3">
@@ -23997,10 +23997,10 @@
         <v>46286</v>
       </c>
       <c r="B895" t="n">
-        <v>37.66575643461045</v>
+        <v>37.61095856967038</v>
       </c>
       <c r="C895" t="n">
-        <v>82.57227262778687</v>
+        <v>82.49835973659792</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13225,10 +13225,10 @@
         <v>46286</v>
       </c>
       <c r="B1170" t="n">
-        <v>125.5699996948242</v>
+        <v>126.4800033569336</v>
       </c>
       <c r="C1170" t="n">
-        <v>222.2100067138672</v>
+        <v>224.0700073242188</v>
       </c>
     </row>
   </sheetData>
@@ -13267,10 +13267,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.374489478632268</v>
+        <v>-0.6597520734401785</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.448008588289639</v>
+        <v>0.3852876593718246</v>
       </c>
     </row>
     <row r="3">
@@ -13928,10 +13928,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>8.278001528905122</v>
+        <v>9.062690373029159</v>
       </c>
       <c r="C2" t="n">
-        <v>4.412178867818262</v>
+        <v>5.286157134118175</v>
       </c>
     </row>
     <row r="3">
@@ -23997,10 +23997,10 @@
         <v>46286</v>
       </c>
       <c r="B895" t="n">
-        <v>37.61095856967038</v>
+        <v>38.60822285691352</v>
       </c>
       <c r="C895" t="n">
-        <v>82.49835973659792</v>
+        <v>84.02595548045353</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13222,13 +13222,13 @@
     </row>
     <row r="1170">
       <c r="A1170" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B1170" t="n">
-        <v>126.4800033569336</v>
+        <v>125</v>
       </c>
       <c r="C1170" t="n">
-        <v>224.0700073242188</v>
+        <v>220.2700042724609</v>
       </c>
     </row>
   </sheetData>
@@ -13267,10 +13267,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.6597520734401785</v>
+        <v>-1.822180097694837</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3852876593718246</v>
+        <v>-1.317146343342501</v>
       </c>
     </row>
     <row r="3">
@@ -13928,10 +13928,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>9.062690373029159</v>
+        <v>7.786495373154168</v>
       </c>
       <c r="C2" t="n">
-        <v>5.286157134118175</v>
+        <v>3.500609290409695</v>
       </c>
     </row>
     <row r="3">
@@ -23994,13 +23994,13 @@
     </row>
     <row r="895">
       <c r="A895" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B895" t="n">
-        <v>38.60822285691352</v>
+        <v>36.98630136986301</v>
       </c>
       <c r="C895" t="n">
-        <v>84.02595548045353</v>
+        <v>80.90505946773318</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1170"/>
+  <dimension ref="A1:C1171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13222,13 +13222,24 @@
     </row>
     <row r="1170">
       <c r="A1170" s="2" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B1170" t="n">
-        <v>125</v>
+        <v>125.5699996948242</v>
       </c>
       <c r="C1170" t="n">
-        <v>220.2700042724609</v>
+        <v>222.2100067138672</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="2" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B1171" t="n">
+        <v>124.7300033569336</v>
+      </c>
+      <c r="C1171" t="n">
+        <v>220.2599945068359</v>
       </c>
     </row>
   </sheetData>
@@ -13267,10 +13278,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.822180097694837</v>
+        <v>-2.034241552072447</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.317146343342501</v>
+        <v>-1.321630804309271</v>
       </c>
     </row>
     <row r="3">
@@ -13928,10 +13939,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>7.786495373154168</v>
+        <v>7.553679437805005</v>
       </c>
       <c r="C2" t="n">
-        <v>3.500609290409695</v>
+        <v>3.495905895390194</v>
       </c>
     </row>
     <row r="3">
@@ -14149,7 +14160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C895"/>
+  <dimension ref="A1:C896"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23994,13 +24005,24 @@
     </row>
     <row r="895">
       <c r="A895" s="2" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B895" t="n">
-        <v>36.98630136986301</v>
+        <v>37.61095856967038</v>
       </c>
       <c r="C895" t="n">
-        <v>80.90505946773318</v>
+        <v>82.49835973659792</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="2" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B896" t="n">
+        <v>36.16812820381479</v>
+      </c>
+      <c r="C896" t="n">
+        <v>79.01494868977986</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1171"/>
+  <dimension ref="A1:C1172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13233,13 +13233,24 @@
     </row>
     <row r="1171">
       <c r="A1171" s="2" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B1171" t="n">
-        <v>124.7300033569336</v>
+        <v>125</v>
       </c>
       <c r="C1171" t="n">
-        <v>220.2599945068359</v>
+        <v>220.2700042724609</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1172" t="n">
+        <v>123.4300003051758</v>
+      </c>
+      <c r="C1172" t="n">
+        <v>215.9499969482422</v>
       </c>
     </row>
   </sheetData>
@@ -13278,10 +13289,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-2.034241552072447</v>
+        <v>-3.055293275975846</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.321630804309271</v>
+        <v>-3.25254672606663</v>
       </c>
     </row>
     <row r="3">
@@ -13939,10 +13950,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>7.553679437805005</v>
+        <v>6.432697254417974</v>
       </c>
       <c r="C2" t="n">
-        <v>3.495905895390194</v>
+        <v>1.470721509399753</v>
       </c>
     </row>
     <row r="3">
@@ -14160,7 +14171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C896"/>
+  <dimension ref="A1:C897"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24016,13 +24027,24 @@
     </row>
     <row r="896">
       <c r="A896" s="2" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B896" t="n">
-        <v>36.16812820381479</v>
+        <v>36.4628843692777</v>
       </c>
       <c r="C896" t="n">
-        <v>79.01494868977986</v>
+        <v>79.02308406490219</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B897" t="n">
+        <v>35.20648380690488</v>
+      </c>
+      <c r="C897" t="n">
+        <v>74.64617410703846</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1172"/>
+  <dimension ref="A1:C1173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13244,13 +13244,24 @@
     </row>
     <row r="1172">
       <c r="A1172" s="2" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B1172" t="n">
-        <v>123.4300003051758</v>
+        <v>124.7300033569336</v>
       </c>
       <c r="C1172" t="n">
-        <v>215.9499969482422</v>
+        <v>220.2599945068359</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1173" t="n">
+        <v>124.4300003051758</v>
+      </c>
+      <c r="C1173" t="n">
+        <v>218.8000030517578</v>
       </c>
     </row>
   </sheetData>
@@ -13289,10 +13300,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-3.055293275975846</v>
+        <v>-2.269870716757405</v>
       </c>
       <c r="C2" t="n">
-        <v>-3.25254672606663</v>
+        <v>-1.975719515013752</v>
       </c>
     </row>
     <row r="3">
@@ -13950,10 +13961,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>6.432697254417974</v>
+        <v>7.294989217403214</v>
       </c>
       <c r="C2" t="n">
-        <v>1.470721509399753</v>
+        <v>2.809884184633482</v>
       </c>
     </row>
     <row r="3">
@@ -14171,7 +14182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C897"/>
+  <dimension ref="A1:C898"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24038,13 +24049,24 @@
     </row>
     <row r="897">
       <c r="A897" s="2" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B897" t="n">
-        <v>35.20648380690488</v>
+        <v>36.63052043602126</v>
       </c>
       <c r="C897" t="n">
-        <v>74.64617410703846</v>
+        <v>78.13181705520429</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B898" t="n">
+        <v>33.59458999417269</v>
+      </c>
+      <c r="C898" t="n">
+        <v>70.64420602768573</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1173"/>
+  <dimension ref="A1:C1174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13255,13 +13255,24 @@
     </row>
     <row r="1173">
       <c r="A1173" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1173" t="n">
+        <v>123.4300003051758</v>
+      </c>
+      <c r="C1173" t="n">
+        <v>215.9499969482422</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="2" t="n">
         <v>46290</v>
       </c>
-      <c r="B1173" t="n">
-        <v>124.4300003051758</v>
-      </c>
-      <c r="C1173" t="n">
-        <v>218.8000030517578</v>
+      <c r="B1174" t="n">
+        <v>123.4300003051758</v>
+      </c>
+      <c r="C1174" t="n">
+        <v>215.9499969482422</v>
       </c>
     </row>
   </sheetData>
@@ -13300,10 +13311,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-2.269870716757405</v>
+        <v>-3.055293275975846</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.975719515013752</v>
+        <v>-3.25254672606663</v>
       </c>
     </row>
     <row r="3">
@@ -13961,10 +13972,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>7.294989217403214</v>
+        <v>6.432697254417974</v>
       </c>
       <c r="C2" t="n">
-        <v>2.809884184633482</v>
+        <v>1.470721509399753</v>
       </c>
     </row>
     <row r="3">
@@ -14182,7 +14193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C898"/>
+  <dimension ref="A1:C899"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24060,13 +24071,24 @@
     </row>
     <row r="898">
       <c r="A898" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B898" t="n">
+        <v>32.52093742110736</v>
+      </c>
+      <c r="C898" t="n">
+        <v>68.42145912674791</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="2" t="n">
         <v>46290</v>
       </c>
-      <c r="B898" t="n">
-        <v>33.59458999417269</v>
-      </c>
-      <c r="C898" t="n">
-        <v>70.64420602768573</v>
+      <c r="B899" t="n">
+        <v>29.74876891499228</v>
+      </c>
+      <c r="C899" t="n">
+        <v>66.44827177814517</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13269,10 +13269,10 @@
         <v>46290</v>
       </c>
       <c r="B1174" t="n">
-        <v>123.4300003051758</v>
+        <v>124.4300003051758</v>
       </c>
       <c r="C1174" t="n">
-        <v>215.9499969482422</v>
+        <v>218.8000030517578</v>
       </c>
     </row>
   </sheetData>
@@ -13311,10 +13311,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-3.055293275975846</v>
+        <v>-2.269870716757405</v>
       </c>
       <c r="C2" t="n">
-        <v>-3.25254672606663</v>
+        <v>-1.975719515013752</v>
       </c>
     </row>
     <row r="3">
@@ -13972,10 +13972,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>6.432697254417974</v>
+        <v>7.294989217403214</v>
       </c>
       <c r="C2" t="n">
-        <v>1.470721509399753</v>
+        <v>2.809884184633482</v>
       </c>
     </row>
     <row r="3">
@@ -24085,10 +24085,10 @@
         <v>46290</v>
       </c>
       <c r="B899" t="n">
-        <v>29.74876891499228</v>
+        <v>30.79996204951543</v>
       </c>
       <c r="C899" t="n">
-        <v>66.44827177814517</v>
+        <v>68.64497748405466</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1174"/>
+  <dimension ref="A1:C1175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13273,6 +13273,17 @@
       </c>
       <c r="C1174" t="n">
         <v>218.8000030517578</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1175" t="n">
+        <v>121.1699981689453</v>
+      </c>
+      <c r="C1175" t="n">
+        <v>210.6499938964844</v>
       </c>
     </row>
   </sheetData>
@@ -13311,10 +13322,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-2.269870716757405</v>
+        <v>-4.830349937653134</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.975719515013752</v>
+        <v>-5.626993611215414</v>
       </c>
     </row>
     <row r="3">
@@ -13972,10 +13983,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>7.294989217403214</v>
+        <v>4.483915576016972</v>
       </c>
       <c r="C2" t="n">
-        <v>2.809884184633482</v>
+        <v>-1.019647285524472</v>
       </c>
     </row>
     <row r="3">
@@ -14193,7 +14204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C899"/>
+  <dimension ref="A1:C900"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24089,6 +24100,17 @@
       </c>
       <c r="C899" t="n">
         <v>68.64497748405466</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B900" t="n">
+        <v>28.03254326964701</v>
+      </c>
+      <c r="C900" t="n">
+        <v>62.05091545100525</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13280,10 +13280,10 @@
         <v>46293</v>
       </c>
       <c r="B1175" t="n">
-        <v>121.1699981689453</v>
+        <v>124.4300003051758</v>
       </c>
       <c r="C1175" t="n">
-        <v>210.6499938964844</v>
+        <v>218.8000030517578</v>
       </c>
     </row>
   </sheetData>
@@ -13322,10 +13322,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.830349937653134</v>
+        <v>-2.269870716757405</v>
       </c>
       <c r="C2" t="n">
-        <v>-5.626993611215414</v>
+        <v>-1.975719515013752</v>
       </c>
     </row>
     <row r="3">
@@ -13983,10 +13983,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>4.483915576016972</v>
+        <v>7.294989217403214</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.019647285524472</v>
+        <v>2.809884184633482</v>
       </c>
     </row>
     <row r="3">
@@ -24107,10 +24107,10 @@
         <v>46293</v>
       </c>
       <c r="B900" t="n">
-        <v>28.03254326964701</v>
+        <v>31.47717783986559</v>
       </c>
       <c r="C900" t="n">
-        <v>62.05091545100525</v>
+        <v>68.32063528396735</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13277,13 +13277,13 @@
     </row>
     <row r="1175">
       <c r="A1175" s="2" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B1175" t="n">
-        <v>124.4300003051758</v>
+        <v>120.6399993896484</v>
       </c>
       <c r="C1175" t="n">
-        <v>218.8000030517578</v>
+        <v>209.1499938964844</v>
       </c>
     </row>
   </sheetData>
@@ -13322,10 +13322,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-2.269870716757405</v>
+        <v>-5.246622935271128</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.975719515013752</v>
+        <v>-6.299006493649872</v>
       </c>
     </row>
     <row r="3">
@@ -13983,10 +13983,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>7.294989217403214</v>
+        <v>4.026901888237289</v>
       </c>
       <c r="C2" t="n">
-        <v>2.809884184633482</v>
+        <v>-1.724468236740229</v>
       </c>
     </row>
     <row r="3">
@@ -24104,13 +24104,13 @@
     </row>
     <row r="900">
       <c r="A900" s="2" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B900" t="n">
-        <v>31.47717783986559</v>
+        <v>27.47252764970309</v>
       </c>
       <c r="C900" t="n">
-        <v>68.32063528396735</v>
+        <v>60.89698058169801</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13280,10 +13280,10 @@
         <v>46294</v>
       </c>
       <c r="B1175" t="n">
-        <v>120.6399993896484</v>
+        <v>124.4300003051758</v>
       </c>
       <c r="C1175" t="n">
-        <v>209.1499938964844</v>
+        <v>218.8000030517578</v>
       </c>
     </row>
   </sheetData>
@@ -13322,10 +13322,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-5.246622935271128</v>
+        <v>-2.269870716757405</v>
       </c>
       <c r="C2" t="n">
-        <v>-6.299006493649872</v>
+        <v>-1.975719515013752</v>
       </c>
     </row>
     <row r="3">
@@ -13983,10 +13983,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>4.026901888237289</v>
+        <v>7.294989217403214</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.724468236740229</v>
+        <v>2.809884184633482</v>
       </c>
     </row>
     <row r="3">
@@ -24107,10 +24107,10 @@
         <v>46294</v>
       </c>
       <c r="B900" t="n">
-        <v>27.47252764970309</v>
+        <v>31.47717783986559</v>
       </c>
       <c r="C900" t="n">
-        <v>60.89698058169801</v>
+        <v>68.32063528396735</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1175"/>
+  <dimension ref="A1:C1176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13277,13 +13277,24 @@
     </row>
     <row r="1175">
       <c r="A1175" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="B1175" t="n">
-        <v>124.4300003051758</v>
+        <v>121.1699981689453</v>
       </c>
       <c r="C1175" t="n">
-        <v>218.8000030517578</v>
+        <v>210.6499938964844</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1176" t="n">
+        <v>121.5899963378906</v>
+      </c>
+      <c r="C1176" t="n">
+        <v>209.6199951171875</v>
       </c>
     </row>
   </sheetData>
@@ -13322,10 +13333,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-2.269870716757405</v>
+        <v>-4.500473900933044</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.975719515013752</v>
+        <v>-6.08844191026826</v>
       </c>
     </row>
     <row r="3">
@@ -13983,10 +13994,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>7.294989217403214</v>
+        <v>4.846076621567041</v>
       </c>
       <c r="C2" t="n">
-        <v>2.809884184633482</v>
+        <v>-1.503623765107864</v>
       </c>
     </row>
     <row r="3">
@@ -14204,7 +14215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C900"/>
+  <dimension ref="A1:C901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24104,13 +24115,24 @@
     </row>
     <row r="900">
       <c r="A900" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="B900" t="n">
-        <v>31.47717783986559</v>
+        <v>28.03254326964701</v>
       </c>
       <c r="C900" t="n">
-        <v>68.32063528396735</v>
+        <v>62.05091545100525</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B901" t="n">
+        <v>28.76204166572069</v>
+      </c>
+      <c r="C901" t="n">
+        <v>58.35914697406339</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13291,10 +13291,10 @@
         <v>46295</v>
       </c>
       <c r="B1176" t="n">
-        <v>121.5899963378906</v>
+        <v>121.1699981689453</v>
       </c>
       <c r="C1176" t="n">
-        <v>209.6199951171875</v>
+        <v>210.6499938964844</v>
       </c>
     </row>
   </sheetData>
@@ -13333,10 +13333,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.500473900933044</v>
+        <v>-4.830349937653134</v>
       </c>
       <c r="C2" t="n">
-        <v>-6.08844191026826</v>
+        <v>-5.626993611215414</v>
       </c>
     </row>
     <row r="3">
@@ -13994,10 +13994,10 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>4.846076621567041</v>
+        <v>4.483915576016972</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.503623765107864</v>
+        <v>-1.019647285524472</v>
       </c>
     </row>
     <row r="3">
@@ -24129,10 +24129,10 @@
         <v>46295</v>
       </c>
       <c r="B901" t="n">
-        <v>28.76204166572069</v>
+        <v>28.31726969962096</v>
       </c>
       <c r="C901" t="n">
-        <v>58.35914697406339</v>
+        <v>59.13726801152739</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1176"/>
+  <dimension ref="A1:C1177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13288,13 +13288,24 @@
     </row>
     <row r="1176">
       <c r="A1176" s="2" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="B1176" t="n">
-        <v>121.1699981689453</v>
+        <v>120.6399993896484</v>
       </c>
       <c r="C1176" t="n">
-        <v>210.6499938964844</v>
+        <v>209.1499938964844</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1177" t="n">
+        <v>121.4300003051758</v>
+      </c>
+      <c r="C1177" t="n">
+        <v>208.7100067138672</v>
       </c>
     </row>
   </sheetData>
@@ -13308,7 +13319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13330,619 +13341,630 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.830349937653134</v>
+        <v>0.6548416110114141</v>
       </c>
       <c r="C2" t="n">
-        <v>-5.626993611215414</v>
+        <v>-0.2103692065298146</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="B3" t="n">
-        <v>8.71829820789034</v>
+        <v>-5.246622935271128</v>
       </c>
       <c r="C3" t="n">
-        <v>8.086781585032888</v>
+        <v>-6.299006493649872</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9830123115019296</v>
+        <v>8.71829820789034</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.964952824087574</v>
+        <v>8.086781585032888</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B5" t="n">
-        <v>-9.85619376397635</v>
+        <v>0.9830123115019296</v>
       </c>
       <c r="C5" t="n">
-        <v>-14.65693086924618</v>
+        <v>-2.964952824087574</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B6" t="n">
-        <v>4.229112515921862</v>
+        <v>-9.85619376397635</v>
       </c>
       <c r="C6" t="n">
-        <v>9.613184666895602</v>
+        <v>-14.65693086924618</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B7" t="n">
-        <v>1.84833552161412</v>
+        <v>4.229112515921862</v>
       </c>
       <c r="C7" t="n">
-        <v>5.285078707965862</v>
+        <v>9.613184666895602</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B8" t="n">
-        <v>-7.910336762386572</v>
+        <v>1.84833552161412</v>
       </c>
       <c r="C8" t="n">
-        <v>-14.52869589108167</v>
+        <v>5.285078707965862</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3660852686114824</v>
+        <v>-7.910336762386572</v>
       </c>
       <c r="C9" t="n">
-        <v>-11.75300619118631</v>
+        <v>-14.52869589108167</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B10" t="n">
-        <v>19.08091398635481</v>
+        <v>0.3660852686114824</v>
       </c>
       <c r="C10" t="n">
-        <v>32.98056014766524</v>
+        <v>-11.75300619118631</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B11" t="n">
-        <v>5.247560427873244</v>
+        <v>19.08091398635481</v>
       </c>
       <c r="C11" t="n">
-        <v>37.41786490059109</v>
+        <v>32.98056014766524</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B12" t="n">
-        <v>4.599086440615774</v>
+        <v>5.247560427873244</v>
       </c>
       <c r="C12" t="n">
-        <v>10.0372028702417</v>
+        <v>37.41786490059109</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B13" t="n">
-        <v>4.350545889754165</v>
+        <v>4.599086440615774</v>
       </c>
       <c r="C13" t="n">
-        <v>4.703456714920939</v>
+        <v>10.0372028702417</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B14" t="n">
-        <v>12.3154471376091</v>
+        <v>4.350545889754165</v>
       </c>
       <c r="C14" t="n">
-        <v>19.80102582373344</v>
+        <v>4.703456714920939</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B15" t="n">
-        <v>3.819950737498878</v>
+        <v>12.3154471376091</v>
       </c>
       <c r="C15" t="n">
-        <v>6.24883087916388</v>
+        <v>19.80102582373344</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B16" t="n">
-        <v>2.762844284902344</v>
+        <v>3.819950737498878</v>
       </c>
       <c r="C16" t="n">
-        <v>4.323216797503804</v>
+        <v>6.24883087916388</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B17" t="n">
-        <v>0.6290099552611617</v>
+        <v>2.762844284902344</v>
       </c>
       <c r="C17" t="n">
-        <v>8.606256362377396</v>
+        <v>4.323216797503804</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5057548924013222</v>
+        <v>0.6290099552611617</v>
       </c>
       <c r="C18" t="n">
-        <v>2.979694003164512</v>
+        <v>8.606256362377396</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B19" t="n">
-        <v>6.647778360750189</v>
+        <v>0.5057548924013222</v>
       </c>
       <c r="C19" t="n">
-        <v>-6.127044898596667</v>
+        <v>2.979694003164512</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B20" t="n">
-        <v>4.303804857467131</v>
+        <v>6.647778360750189</v>
       </c>
       <c r="C20" t="n">
-        <v>7.89299078256791</v>
+        <v>-6.127044898596667</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B21" t="n">
-        <v>2.924140980781398</v>
+        <v>4.303804857467131</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.2316081269587822</v>
+        <v>7.89299078256791</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B22" t="n">
-        <v>7.785935057409143</v>
+        <v>2.924140980781398</v>
       </c>
       <c r="C22" t="n">
-        <v>8.288539990171895</v>
+        <v>-0.2316081269587822</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.3110974876163297</v>
+        <v>7.785935057409143</v>
       </c>
       <c r="C23" t="n">
-        <v>-3.670035526014814</v>
+        <v>8.288539990171895</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B24" t="n">
-        <v>-3.930061753406378</v>
+        <v>-0.3110974876163297</v>
       </c>
       <c r="C24" t="n">
-        <v>-7.79675266346972</v>
+        <v>-3.670035526014814</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B25" t="n">
-        <v>5.302909476542483</v>
+        <v>-3.930061753406378</v>
       </c>
       <c r="C25" t="n">
-        <v>7.076324014940227</v>
+        <v>-7.79675266346972</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B26" t="n">
-        <v>4.764258814569922</v>
+        <v>5.302909476542483</v>
       </c>
       <c r="C26" t="n">
-        <v>5.982907474372823</v>
+        <v>7.076324014940227</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B27" t="n">
-        <v>3.374232331184368</v>
+        <v>4.764258814569922</v>
       </c>
       <c r="C27" t="n">
-        <v>1.502936720396852</v>
+        <v>5.982907474372823</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B28" t="n">
-        <v>-3.216230791005115</v>
+        <v>3.374232331184368</v>
       </c>
       <c r="C28" t="n">
-        <v>-4.726432032443128</v>
+        <v>1.502936720396852</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B29" t="n">
-        <v>-1.076847507836964</v>
+        <v>-3.216230791005115</v>
       </c>
       <c r="C29" t="n">
-        <v>-5.187634688078601</v>
+        <v>-4.726432032443128</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B30" t="n">
-        <v>0.6734557165223753</v>
+        <v>-1.076847507836964</v>
       </c>
       <c r="C30" t="n">
-        <v>15.32586722211562</v>
+        <v>-5.187634688078601</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B31" t="n">
-        <v>7.54283768190398</v>
+        <v>0.6734557165223753</v>
       </c>
       <c r="C31" t="n">
-        <v>8.4783202773973</v>
+        <v>15.32586722211562</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B32" t="n">
-        <v>7.25654020393236</v>
+        <v>7.54283768190398</v>
       </c>
       <c r="C32" t="n">
-        <v>6.047733486673468</v>
+        <v>8.4783202773973</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B33" t="n">
-        <v>-1.068415578494741</v>
+        <v>7.25654020393236</v>
       </c>
       <c r="C33" t="n">
-        <v>-3.258245561246353</v>
+        <v>6.047733486673468</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.5777140778466916</v>
+        <v>-1.068415578494741</v>
       </c>
       <c r="C34" t="n">
-        <v>-2.202831754727963</v>
+        <v>-3.258245561246353</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B35" t="n">
-        <v>0.9595452622609635</v>
+        <v>-0.5777140778466916</v>
       </c>
       <c r="C35" t="n">
-        <v>-3.256936449935688</v>
+        <v>-2.202831754727963</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B36" t="n">
-        <v>2.093738232490927</v>
+        <v>0.9595452622609635</v>
       </c>
       <c r="C36" t="n">
-        <v>5.025337343490821</v>
+        <v>-3.256936449935688</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B37" t="n">
-        <v>5.619802001040464</v>
+        <v>2.093738232490927</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6802768899403677</v>
+        <v>5.025337343490821</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B38" t="n">
-        <v>-2.105258372825114</v>
+        <v>5.619802001040464</v>
       </c>
       <c r="C38" t="n">
-        <v>-3.724932900574174</v>
+        <v>0.6802768899403677</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.6119253340401531</v>
+        <v>-2.105258372825114</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8392963783575125</v>
+        <v>-3.724932900574174</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B40" t="n">
-        <v>2.737778212377684</v>
+        <v>-0.6119253340401531</v>
       </c>
       <c r="C40" t="n">
-        <v>7.562528686444536</v>
+        <v>0.8392963783575125</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B41" t="n">
-        <v>-3.559553406618587</v>
+        <v>2.737778212377684</v>
       </c>
       <c r="C41" t="n">
-        <v>-3.71900911798525</v>
+        <v>7.562528686444536</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.234144257336133</v>
+        <v>-3.559553406618587</v>
       </c>
       <c r="C42" t="n">
-        <v>-3.968255956784306</v>
+        <v>-3.71900911798525</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B43" t="n">
-        <v>0.3524580110659814</v>
+        <v>-0.234144257336133</v>
       </c>
       <c r="C43" t="n">
-        <v>3.410221769566157</v>
+        <v>-3.968255956784306</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B44" t="n">
-        <v>7.719890021497</v>
+        <v>0.3524580110659814</v>
       </c>
       <c r="C44" t="n">
-        <v>13.10819252034816</v>
+        <v>3.410221769566157</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B45" t="n">
-        <v>-2.588860425183181</v>
+        <v>7.719890021497</v>
       </c>
       <c r="C45" t="n">
-        <v>-6.718428768534002</v>
+        <v>13.10819252034816</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B46" t="n">
-        <v>4.01794660532715</v>
+        <v>-2.588860425183181</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.3718577830090442</v>
+        <v>-6.718428768534002</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B47" t="n">
-        <v>3.747233921473403</v>
+        <v>4.01794660532715</v>
       </c>
       <c r="C47" t="n">
-        <v>9.63797079504587</v>
+        <v>-0.3718577830090442</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B48" t="n">
-        <v>4.325697320578858</v>
+        <v>3.747233921473403</v>
       </c>
       <c r="C48" t="n">
-        <v>7.371737067902551</v>
+        <v>9.63797079504587</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1621865038732517</v>
+        <v>4.325697320578858</v>
       </c>
       <c r="C49" t="n">
-        <v>1.764080002332857</v>
+        <v>7.371737067902551</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B50" t="n">
-        <v>-1.685652967530238</v>
+        <v>0.1621865038732517</v>
       </c>
       <c r="C50" t="n">
-        <v>3.237671636813877</v>
+        <v>1.764080002332857</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.3631408134932568</v>
+        <v>-1.685652967530238</v>
       </c>
       <c r="C51" t="n">
-        <v>-5.296168701592718</v>
+        <v>3.237671636813877</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B52" t="n">
-        <v>0.6855645869853433</v>
+        <v>-0.3631408134932568</v>
       </c>
       <c r="C52" t="n">
-        <v>-2.662370124342184</v>
+        <v>-5.296168701592718</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.4323149900067103</v>
+        <v>0.6855645869853433</v>
       </c>
       <c r="C53" t="n">
-        <v>-3.848036099611796</v>
+        <v>-2.662370124342184</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B54" t="n">
-        <v>-1.875418922567351</v>
+        <v>-0.4323149900067103</v>
       </c>
       <c r="C54" t="n">
-        <v>-5.017806843863504</v>
+        <v>-3.848036099611796</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B55" t="n">
-        <v>1.518590208211412</v>
+        <v>-1.875418922567351</v>
       </c>
       <c r="C55" t="n">
-        <v>-2.609356376021654</v>
+        <v>-5.017806843863504</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B56" t="n">
-        <v>1.215872396057804</v>
+        <v>1.518590208211412</v>
       </c>
       <c r="C56" t="n">
-        <v>2.235936178495601</v>
+        <v>-2.609356376021654</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B57" t="n">
-        <v>5.67272764263731</v>
+        <v>1.215872396057804</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2.235936178495601</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
+        <v>44620</v>
+      </c>
+      <c r="B58" t="n">
+        <v>5.67272764263731</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
         <v>44592</v>
       </c>
     </row>
@@ -13969,7 +13991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13991,204 +14013,215 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46295</v>
+        <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>4.483915576016972</v>
+        <v>0.6548416110114141</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.019647285524472</v>
+        <v>-0.2103692065298146</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="B3" t="n">
-        <v>-4.307287000201954</v>
+        <v>4.026901888237289</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.508697926328606</v>
+        <v>-1.724468236740229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="B4" t="n">
-        <v>10.06266621527294</v>
+        <v>-4.307287000201954</v>
       </c>
       <c r="C4" t="n">
-        <v>0.301726397146429</v>
+        <v>-1.508697926328606</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46022</v>
+        <v>46112</v>
       </c>
       <c r="B5" t="n">
-        <v>14.87741508945415</v>
+        <v>10.06266621527294</v>
       </c>
       <c r="C5" t="n">
-        <v>58.32290812072105</v>
+        <v>0.301726397146429</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45930</v>
+        <v>46022</v>
       </c>
       <c r="B6" t="n">
-        <v>19.82747972735621</v>
+        <v>14.87741508945415</v>
       </c>
       <c r="C6" t="n">
-        <v>32.79009046866983</v>
+        <v>58.32290812072105</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45838</v>
+        <v>45930</v>
       </c>
       <c r="B7" t="n">
-        <v>7.861372591380933</v>
+        <v>19.82747972735621</v>
       </c>
       <c r="C7" t="n">
-        <v>4.989756990491467</v>
+        <v>32.79009046866983</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45747</v>
+        <v>45838</v>
       </c>
       <c r="B8" t="n">
-        <v>15.71229193262609</v>
+        <v>7.861372591380933</v>
       </c>
       <c r="C8" t="n">
-        <v>16.56514339078781</v>
+        <v>4.989756990491467</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45657</v>
+        <v>45747</v>
       </c>
       <c r="B9" t="n">
-        <v>0.8497200744499223</v>
+        <v>15.71229193262609</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.895499220552157</v>
+        <v>16.56514339078781</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45565</v>
+        <v>45657</v>
       </c>
       <c r="B10" t="n">
-        <v>4.816094536539461</v>
+        <v>0.8497200744499223</v>
       </c>
       <c r="C10" t="n">
-        <v>2.49126816255496</v>
+        <v>-4.895499220552157</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45473</v>
+        <v>45565</v>
       </c>
       <c r="B11" t="n">
-        <v>7.101219597988462</v>
+        <v>4.816094536539461</v>
       </c>
       <c r="C11" t="n">
-        <v>18.613647746147</v>
+        <v>2.49126816255496</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45382</v>
+        <v>45473</v>
       </c>
       <c r="B12" t="n">
-        <v>5.497578776235734</v>
+        <v>7.101219597988462</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3324991171443914</v>
+        <v>18.613647746147</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45291</v>
+        <v>45382</v>
       </c>
       <c r="B13" t="n">
-        <v>8.865893387533141</v>
+        <v>5.497578776235734</v>
       </c>
       <c r="C13" t="n">
-        <v>2.295922339335066</v>
+        <v>0.3324991171443914</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45199</v>
+        <v>45291</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.04056065140266574</v>
+        <v>8.865893387533141</v>
       </c>
       <c r="C14" t="n">
-        <v>4.425037557012979</v>
+        <v>2.295922339335066</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45107</v>
+        <v>45199</v>
       </c>
       <c r="B15" t="n">
-        <v>-3.446246978755263</v>
+        <v>-0.04056065140266574</v>
       </c>
       <c r="C15" t="n">
-        <v>-4.38658349291331</v>
+        <v>4.425037557012979</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45016</v>
+        <v>45107</v>
       </c>
       <c r="B16" t="n">
-        <v>9.147250898805925</v>
+        <v>-3.446246978755263</v>
       </c>
       <c r="C16" t="n">
-        <v>5.116755377429172</v>
+        <v>-4.38658349291331</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>44926</v>
+        <v>45016</v>
       </c>
       <c r="B17" t="n">
-        <v>8.41056784279135</v>
+        <v>9.147250898805925</v>
       </c>
       <c r="C17" t="n">
-        <v>19.79687212491488</v>
+        <v>5.116755377429172</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>44834</v>
+        <v>44926</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.371111739339004</v>
+        <v>8.41056784279135</v>
       </c>
       <c r="C18" t="n">
-        <v>-4.832969696154221</v>
+        <v>19.79687212491488</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>44742</v>
+        <v>44834</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.8159578854644911</v>
+        <v>-1.371111739339004</v>
       </c>
       <c r="C19" t="n">
-        <v>-11.05580919103796</v>
+        <v>-4.832969696154221</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
+        <v>44742</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.8159578854644911</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-11.05580919103796</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
         <v>44651</v>
       </c>
     </row>
@@ -14215,7 +14248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C901"/>
+  <dimension ref="A1:C902"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24126,13 +24159,24 @@
     </row>
     <row r="901">
       <c r="A901" s="2" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="B901" t="n">
-        <v>28.31726969962096</v>
+        <v>27.7560086834354</v>
       </c>
       <c r="C901" t="n">
-        <v>59.13726801152739</v>
+        <v>58.00408069164264</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B902" t="n">
+        <v>28.87921750365436</v>
+      </c>
+      <c r="C902" t="n">
+        <v>56.91302558706648</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13302,10 +13302,10 @@
         <v>46296</v>
       </c>
       <c r="B1177" t="n">
-        <v>121.4300003051758</v>
+        <v>120.6399993896484</v>
       </c>
       <c r="C1177" t="n">
-        <v>208.7100067138672</v>
+        <v>209.1499938964844</v>
       </c>
     </row>
   </sheetData>
@@ -13344,10 +13344,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6548416110114141</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2103692065298146</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -14016,10 +14016,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6548416110114141</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2103692065298146</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -24173,10 +24173,10 @@
         <v>46296</v>
       </c>
       <c r="B902" t="n">
-        <v>28.87921750365436</v>
+        <v>28.04075337152512</v>
       </c>
       <c r="C902" t="n">
-        <v>56.91302558706648</v>
+        <v>57.2438181596461</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13299,13 +13299,13 @@
     </row>
     <row r="1177">
       <c r="A1177" s="2" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="B1177" t="n">
-        <v>120.6399993896484</v>
+        <v>121.5899963378906</v>
       </c>
       <c r="C1177" t="n">
-        <v>209.1499938964844</v>
+        <v>209.6199951171875</v>
       </c>
     </row>
   </sheetData>
@@ -13319,7 +13319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13341,630 +13341,619 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-4.500473900933044</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-6.08844191026826</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="B3" t="n">
-        <v>-5.246622935271128</v>
+        <v>8.71829820789034</v>
       </c>
       <c r="C3" t="n">
-        <v>-6.299006493649872</v>
+        <v>8.086781585032888</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B4" t="n">
-        <v>8.71829820789034</v>
+        <v>0.9830123115019296</v>
       </c>
       <c r="C4" t="n">
-        <v>8.086781585032888</v>
+        <v>-2.964952824087574</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9830123115019296</v>
+        <v>-9.85619376397635</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.964952824087574</v>
+        <v>-14.65693086924618</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="B6" t="n">
-        <v>-9.85619376397635</v>
+        <v>4.229112515921862</v>
       </c>
       <c r="C6" t="n">
-        <v>-14.65693086924618</v>
+        <v>9.613184666895602</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="B7" t="n">
-        <v>4.229112515921862</v>
+        <v>1.84833552161412</v>
       </c>
       <c r="C7" t="n">
-        <v>9.613184666895602</v>
+        <v>5.285078707965862</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="B8" t="n">
-        <v>1.84833552161412</v>
+        <v>-7.910336762386572</v>
       </c>
       <c r="C8" t="n">
-        <v>5.285078707965862</v>
+        <v>-14.52869589108167</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46112</v>
+        <v>46081</v>
       </c>
       <c r="B9" t="n">
-        <v>-7.910336762386572</v>
+        <v>0.3660852686114824</v>
       </c>
       <c r="C9" t="n">
-        <v>-14.52869589108167</v>
+        <v>-11.75300619118631</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B10" t="n">
-        <v>0.3660852686114824</v>
+        <v>19.08091398635481</v>
       </c>
       <c r="C10" t="n">
-        <v>-11.75300619118631</v>
+        <v>32.98056014766524</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="B11" t="n">
-        <v>19.08091398635481</v>
+        <v>5.247560427873244</v>
       </c>
       <c r="C11" t="n">
-        <v>32.98056014766524</v>
+        <v>37.41786490059109</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B12" t="n">
-        <v>5.247560427873244</v>
+        <v>4.599086440615774</v>
       </c>
       <c r="C12" t="n">
-        <v>37.41786490059109</v>
+        <v>10.0372028702417</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B13" t="n">
-        <v>4.599086440615774</v>
+        <v>4.350545889754165</v>
       </c>
       <c r="C13" t="n">
-        <v>10.0372028702417</v>
+        <v>4.703456714920939</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="B14" t="n">
-        <v>4.350545889754165</v>
+        <v>12.3154471376091</v>
       </c>
       <c r="C14" t="n">
-        <v>4.703456714920939</v>
+        <v>19.80102582373344</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45930</v>
+        <v>45900</v>
       </c>
       <c r="B15" t="n">
-        <v>12.3154471376091</v>
+        <v>3.819950737498878</v>
       </c>
       <c r="C15" t="n">
-        <v>19.80102582373344</v>
+        <v>6.24883087916388</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45900</v>
+        <v>45869</v>
       </c>
       <c r="B16" t="n">
-        <v>3.819950737498878</v>
+        <v>2.762844284902344</v>
       </c>
       <c r="C16" t="n">
-        <v>6.24883087916388</v>
+        <v>4.323216797503804</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45869</v>
+        <v>45838</v>
       </c>
       <c r="B17" t="n">
-        <v>2.762844284902344</v>
+        <v>0.6290099552611617</v>
       </c>
       <c r="C17" t="n">
-        <v>4.323216797503804</v>
+        <v>8.606256362377396</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45838</v>
+        <v>45808</v>
       </c>
       <c r="B18" t="n">
-        <v>0.6290099552611617</v>
+        <v>0.5057548924013222</v>
       </c>
       <c r="C18" t="n">
-        <v>8.606256362377396</v>
+        <v>2.979694003164512</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45808</v>
+        <v>45777</v>
       </c>
       <c r="B19" t="n">
-        <v>0.5057548924013222</v>
+        <v>6.647778360750189</v>
       </c>
       <c r="C19" t="n">
-        <v>2.979694003164512</v>
+        <v>-6.127044898596667</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45777</v>
+        <v>45747</v>
       </c>
       <c r="B20" t="n">
-        <v>6.647778360750189</v>
+        <v>4.303804857467131</v>
       </c>
       <c r="C20" t="n">
-        <v>-6.127044898596667</v>
+        <v>7.89299078256791</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45747</v>
+        <v>45716</v>
       </c>
       <c r="B21" t="n">
-        <v>4.303804857467131</v>
+        <v>2.924140980781398</v>
       </c>
       <c r="C21" t="n">
-        <v>7.89299078256791</v>
+        <v>-0.2316081269587822</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45716</v>
+        <v>45688</v>
       </c>
       <c r="B22" t="n">
-        <v>2.924140980781398</v>
+        <v>7.785935057409143</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.2316081269587822</v>
+        <v>8.288539990171895</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45688</v>
+        <v>45657</v>
       </c>
       <c r="B23" t="n">
-        <v>7.785935057409143</v>
+        <v>-0.3110974876163297</v>
       </c>
       <c r="C23" t="n">
-        <v>8.288539990171895</v>
+        <v>-3.670035526014814</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45657</v>
+        <v>45626</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.3110974876163297</v>
+        <v>-3.930061753406378</v>
       </c>
       <c r="C24" t="n">
-        <v>-3.670035526014814</v>
+        <v>-7.79675266346972</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45626</v>
+        <v>45596</v>
       </c>
       <c r="B25" t="n">
-        <v>-3.930061753406378</v>
+        <v>5.302909476542483</v>
       </c>
       <c r="C25" t="n">
-        <v>-7.79675266346972</v>
+        <v>7.076324014940227</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45596</v>
+        <v>45565</v>
       </c>
       <c r="B26" t="n">
-        <v>5.302909476542483</v>
+        <v>4.764258814569922</v>
       </c>
       <c r="C26" t="n">
-        <v>7.076324014940227</v>
+        <v>5.982907474372823</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45565</v>
+        <v>45535</v>
       </c>
       <c r="B27" t="n">
-        <v>4.764258814569922</v>
+        <v>3.374232331184368</v>
       </c>
       <c r="C27" t="n">
-        <v>5.982907474372823</v>
+        <v>1.502936720396852</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45535</v>
+        <v>45504</v>
       </c>
       <c r="B28" t="n">
-        <v>3.374232331184368</v>
+        <v>-3.216230791005115</v>
       </c>
       <c r="C28" t="n">
-        <v>1.502936720396852</v>
+        <v>-4.726432032443128</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45504</v>
+        <v>45473</v>
       </c>
       <c r="B29" t="n">
-        <v>-3.216230791005115</v>
+        <v>-1.076847507836964</v>
       </c>
       <c r="C29" t="n">
-        <v>-4.726432032443128</v>
+        <v>-5.187634688078601</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45473</v>
+        <v>45443</v>
       </c>
       <c r="B30" t="n">
-        <v>-1.076847507836964</v>
+        <v>0.6734557165223753</v>
       </c>
       <c r="C30" t="n">
-        <v>-5.187634688078601</v>
+        <v>15.32586722211562</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45443</v>
+        <v>45412</v>
       </c>
       <c r="B31" t="n">
-        <v>0.6734557165223753</v>
+        <v>7.54283768190398</v>
       </c>
       <c r="C31" t="n">
-        <v>15.32586722211562</v>
+        <v>8.4783202773973</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45412</v>
+        <v>45382</v>
       </c>
       <c r="B32" t="n">
-        <v>7.54283768190398</v>
+        <v>7.25654020393236</v>
       </c>
       <c r="C32" t="n">
-        <v>8.4783202773973</v>
+        <v>6.047733486673468</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45382</v>
+        <v>45351</v>
       </c>
       <c r="B33" t="n">
-        <v>7.25654020393236</v>
+        <v>-1.068415578494741</v>
       </c>
       <c r="C33" t="n">
-        <v>6.047733486673468</v>
+        <v>-3.258245561246353</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45351</v>
+        <v>45322</v>
       </c>
       <c r="B34" t="n">
-        <v>-1.068415578494741</v>
+        <v>-0.5777140778466916</v>
       </c>
       <c r="C34" t="n">
-        <v>-3.258245561246353</v>
+        <v>-2.202831754727963</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45322</v>
+        <v>45291</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.5777140778466916</v>
+        <v>0.9595452622609635</v>
       </c>
       <c r="C35" t="n">
-        <v>-2.202831754727963</v>
+        <v>-3.256936449935688</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45291</v>
+        <v>45260</v>
       </c>
       <c r="B36" t="n">
-        <v>0.9595452622609635</v>
+        <v>2.093738232490927</v>
       </c>
       <c r="C36" t="n">
-        <v>-3.256936449935688</v>
+        <v>5.025337343490821</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45260</v>
+        <v>45230</v>
       </c>
       <c r="B37" t="n">
-        <v>2.093738232490927</v>
+        <v>5.619802001040464</v>
       </c>
       <c r="C37" t="n">
-        <v>5.025337343490821</v>
+        <v>0.6802768899403677</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45230</v>
+        <v>45199</v>
       </c>
       <c r="B38" t="n">
-        <v>5.619802001040464</v>
+        <v>-2.105258372825114</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6802768899403677</v>
+        <v>-3.724932900574174</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45199</v>
+        <v>45169</v>
       </c>
       <c r="B39" t="n">
-        <v>-2.105258372825114</v>
+        <v>-0.6119253340401531</v>
       </c>
       <c r="C39" t="n">
-        <v>-3.724932900574174</v>
+        <v>0.8392963783575125</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45169</v>
+        <v>45138</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.6119253340401531</v>
+        <v>2.737778212377684</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8392963783575125</v>
+        <v>7.562528686444536</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45138</v>
+        <v>45107</v>
       </c>
       <c r="B41" t="n">
-        <v>2.737778212377684</v>
+        <v>-3.559553406618587</v>
       </c>
       <c r="C41" t="n">
-        <v>7.562528686444536</v>
+        <v>-3.71900911798525</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45107</v>
+        <v>45077</v>
       </c>
       <c r="B42" t="n">
-        <v>-3.559553406618587</v>
+        <v>-0.234144257336133</v>
       </c>
       <c r="C42" t="n">
-        <v>-3.71900911798525</v>
+        <v>-3.968255956784306</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45077</v>
+        <v>45046</v>
       </c>
       <c r="B43" t="n">
-        <v>-0.234144257336133</v>
+        <v>0.3524580110659814</v>
       </c>
       <c r="C43" t="n">
-        <v>-3.968255956784306</v>
+        <v>3.410221769566157</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45046</v>
+        <v>45016</v>
       </c>
       <c r="B44" t="n">
-        <v>0.3524580110659814</v>
+        <v>7.719890021497</v>
       </c>
       <c r="C44" t="n">
-        <v>3.410221769566157</v>
+        <v>13.10819252034816</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45016</v>
+        <v>44985</v>
       </c>
       <c r="B45" t="n">
-        <v>7.719890021497</v>
+        <v>-2.588860425183181</v>
       </c>
       <c r="C45" t="n">
-        <v>13.10819252034816</v>
+        <v>-6.718428768534002</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>44985</v>
+        <v>44957</v>
       </c>
       <c r="B46" t="n">
-        <v>-2.588860425183181</v>
+        <v>4.01794660532715</v>
       </c>
       <c r="C46" t="n">
-        <v>-6.718428768534002</v>
+        <v>-0.3718577830090442</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>44957</v>
+        <v>44926</v>
       </c>
       <c r="B47" t="n">
-        <v>4.01794660532715</v>
+        <v>3.747233921473403</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.3718577830090442</v>
+        <v>9.63797079504587</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>44926</v>
+        <v>44895</v>
       </c>
       <c r="B48" t="n">
-        <v>3.747233921473403</v>
+        <v>4.325697320578858</v>
       </c>
       <c r="C48" t="n">
-        <v>9.63797079504587</v>
+        <v>7.371737067902551</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>44895</v>
+        <v>44865</v>
       </c>
       <c r="B49" t="n">
-        <v>4.325697320578858</v>
+        <v>0.1621865038732517</v>
       </c>
       <c r="C49" t="n">
-        <v>7.371737067902551</v>
+        <v>1.764080002332857</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>44865</v>
+        <v>44834</v>
       </c>
       <c r="B50" t="n">
-        <v>0.1621865038732517</v>
+        <v>-1.685652967530238</v>
       </c>
       <c r="C50" t="n">
-        <v>1.764080002332857</v>
+        <v>3.237671636813877</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>44834</v>
+        <v>44804</v>
       </c>
       <c r="B51" t="n">
-        <v>-1.685652967530238</v>
+        <v>-0.3631408134932568</v>
       </c>
       <c r="C51" t="n">
-        <v>3.237671636813877</v>
+        <v>-5.296168701592718</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>44804</v>
+        <v>44773</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.3631408134932568</v>
+        <v>0.6855645869853433</v>
       </c>
       <c r="C52" t="n">
-        <v>-5.296168701592718</v>
+        <v>-2.662370124342184</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>44773</v>
+        <v>44742</v>
       </c>
       <c r="B53" t="n">
-        <v>0.6855645869853433</v>
+        <v>-0.4323149900067103</v>
       </c>
       <c r="C53" t="n">
-        <v>-2.662370124342184</v>
+        <v>-3.848036099611796</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>44742</v>
+        <v>44712</v>
       </c>
       <c r="B54" t="n">
-        <v>-0.4323149900067103</v>
+        <v>-1.875418922567351</v>
       </c>
       <c r="C54" t="n">
-        <v>-3.848036099611796</v>
+        <v>-5.017806843863504</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>44712</v>
+        <v>44681</v>
       </c>
       <c r="B55" t="n">
-        <v>-1.875418922567351</v>
+        <v>1.518590208211412</v>
       </c>
       <c r="C55" t="n">
-        <v>-5.017806843863504</v>
+        <v>-2.609356376021654</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>44681</v>
+        <v>44651</v>
       </c>
       <c r="B56" t="n">
-        <v>1.518590208211412</v>
+        <v>1.215872396057804</v>
       </c>
       <c r="C56" t="n">
-        <v>-2.609356376021654</v>
+        <v>2.235936178495601</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>44651</v>
+        <v>44620</v>
       </c>
       <c r="B57" t="n">
-        <v>1.215872396057804</v>
-      </c>
-      <c r="C57" t="n">
-        <v>2.235936178495601</v>
+        <v>5.67272764263731</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>44620</v>
-      </c>
-      <c r="B58" t="n">
-        <v>5.67272764263731</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
         <v>44592</v>
       </c>
     </row>
@@ -13991,7 +13980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14013,215 +14002,204 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46387</v>
+        <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4.846076621567041</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-1.503623765107864</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46295</v>
+        <v>46203</v>
       </c>
       <c r="B3" t="n">
-        <v>4.026901888237289</v>
+        <v>-4.307287000201954</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.724468236740229</v>
+        <v>-1.508697926328606</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46203</v>
+        <v>46112</v>
       </c>
       <c r="B4" t="n">
-        <v>-4.307287000201954</v>
+        <v>10.06266621527294</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.508697926328606</v>
+        <v>0.301726397146429</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46112</v>
+        <v>46022</v>
       </c>
       <c r="B5" t="n">
-        <v>10.06266621527294</v>
+        <v>14.87741508945415</v>
       </c>
       <c r="C5" t="n">
-        <v>0.301726397146429</v>
+        <v>58.32290812072105</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46022</v>
+        <v>45930</v>
       </c>
       <c r="B6" t="n">
-        <v>14.87741508945415</v>
+        <v>19.82747972735621</v>
       </c>
       <c r="C6" t="n">
-        <v>58.32290812072105</v>
+        <v>32.79009046866983</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45930</v>
+        <v>45838</v>
       </c>
       <c r="B7" t="n">
-        <v>19.82747972735621</v>
+        <v>7.861372591380933</v>
       </c>
       <c r="C7" t="n">
-        <v>32.79009046866983</v>
+        <v>4.989756990491467</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45838</v>
+        <v>45747</v>
       </c>
       <c r="B8" t="n">
-        <v>7.861372591380933</v>
+        <v>15.71229193262609</v>
       </c>
       <c r="C8" t="n">
-        <v>4.989756990491467</v>
+        <v>16.56514339078781</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45747</v>
+        <v>45657</v>
       </c>
       <c r="B9" t="n">
-        <v>15.71229193262609</v>
+        <v>0.8497200744499223</v>
       </c>
       <c r="C9" t="n">
-        <v>16.56514339078781</v>
+        <v>-4.895499220552157</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45657</v>
+        <v>45565</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8497200744499223</v>
+        <v>4.816094536539461</v>
       </c>
       <c r="C10" t="n">
-        <v>-4.895499220552157</v>
+        <v>2.49126816255496</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45565</v>
+        <v>45473</v>
       </c>
       <c r="B11" t="n">
-        <v>4.816094536539461</v>
+        <v>7.101219597988462</v>
       </c>
       <c r="C11" t="n">
-        <v>2.49126816255496</v>
+        <v>18.613647746147</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45473</v>
+        <v>45382</v>
       </c>
       <c r="B12" t="n">
-        <v>7.101219597988462</v>
+        <v>5.497578776235734</v>
       </c>
       <c r="C12" t="n">
-        <v>18.613647746147</v>
+        <v>0.3324991171443914</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45382</v>
+        <v>45291</v>
       </c>
       <c r="B13" t="n">
-        <v>5.497578776235734</v>
+        <v>8.865893387533141</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3324991171443914</v>
+        <v>2.295922339335066</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45291</v>
+        <v>45199</v>
       </c>
       <c r="B14" t="n">
-        <v>8.865893387533141</v>
+        <v>-0.04056065140266574</v>
       </c>
       <c r="C14" t="n">
-        <v>2.295922339335066</v>
+        <v>4.425037557012979</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45199</v>
+        <v>45107</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.04056065140266574</v>
+        <v>-3.446246978755263</v>
       </c>
       <c r="C15" t="n">
-        <v>4.425037557012979</v>
+        <v>-4.38658349291331</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45107</v>
+        <v>45016</v>
       </c>
       <c r="B16" t="n">
-        <v>-3.446246978755263</v>
+        <v>9.147250898805925</v>
       </c>
       <c r="C16" t="n">
-        <v>-4.38658349291331</v>
+        <v>5.116755377429172</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45016</v>
+        <v>44926</v>
       </c>
       <c r="B17" t="n">
-        <v>9.147250898805925</v>
+        <v>8.41056784279135</v>
       </c>
       <c r="C17" t="n">
-        <v>5.116755377429172</v>
+        <v>19.79687212491488</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>44926</v>
+        <v>44834</v>
       </c>
       <c r="B18" t="n">
-        <v>8.41056784279135</v>
+        <v>-1.371111739339004</v>
       </c>
       <c r="C18" t="n">
-        <v>19.79687212491488</v>
+        <v>-4.832969696154221</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>44834</v>
+        <v>44742</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.371111739339004</v>
+        <v>-0.8159578854644911</v>
       </c>
       <c r="C19" t="n">
-        <v>-4.832969696154221</v>
+        <v>-11.05580919103796</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>44742</v>
-      </c>
-      <c r="B20" t="n">
-        <v>-0.8159578854644911</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-11.05580919103796</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
         <v>44651</v>
       </c>
     </row>
@@ -24170,13 +24148,13 @@
     </row>
     <row r="902">
       <c r="A902" s="2" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="B902" t="n">
-        <v>28.04075337152512</v>
+        <v>29.04902861662608</v>
       </c>
       <c r="C902" t="n">
-        <v>57.2438181596461</v>
+        <v>57.59717598245165</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1177"/>
+  <dimension ref="A1:C1179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13306,6 +13306,28 @@
       </c>
       <c r="C1177" t="n">
         <v>209.6199951171875</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1178" t="n">
+        <v>121.4300003051758</v>
+      </c>
+      <c r="C1178" t="n">
+        <v>208.7100067138672</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1179" t="n">
+        <v>121.4300003051758</v>
+      </c>
+      <c r="C1179" t="n">
+        <v>208.7100067138672</v>
       </c>
     </row>
   </sheetData>
@@ -13319,7 +13341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13341,619 +13363,630 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.500473900933044</v>
+        <v>-0.1315865100202984</v>
       </c>
       <c r="C2" t="n">
-        <v>-6.08844191026826</v>
+        <v>-0.4341133596590274</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="B3" t="n">
-        <v>8.71829820789034</v>
+        <v>-4.500473900933044</v>
       </c>
       <c r="C3" t="n">
-        <v>8.086781585032888</v>
+        <v>-6.08844191026826</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9830123115019296</v>
+        <v>8.71829820789034</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.964952824087574</v>
+        <v>8.086781585032888</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B5" t="n">
-        <v>-9.85619376397635</v>
+        <v>0.9830123115019296</v>
       </c>
       <c r="C5" t="n">
-        <v>-14.65693086924618</v>
+        <v>-2.964952824087574</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B6" t="n">
-        <v>4.229112515921862</v>
+        <v>-9.85619376397635</v>
       </c>
       <c r="C6" t="n">
-        <v>9.613184666895602</v>
+        <v>-14.65693086924618</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B7" t="n">
-        <v>1.84833552161412</v>
+        <v>4.229112515921862</v>
       </c>
       <c r="C7" t="n">
-        <v>5.285078707965862</v>
+        <v>9.613184666895602</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B8" t="n">
-        <v>-7.910336762386572</v>
+        <v>1.84833552161412</v>
       </c>
       <c r="C8" t="n">
-        <v>-14.52869589108167</v>
+        <v>5.285078707965862</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3660852686114824</v>
+        <v>-7.910336762386572</v>
       </c>
       <c r="C9" t="n">
-        <v>-11.75300619118631</v>
+        <v>-14.52869589108167</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B10" t="n">
-        <v>19.08091398635481</v>
+        <v>0.3660852686114824</v>
       </c>
       <c r="C10" t="n">
-        <v>32.98056014766524</v>
+        <v>-11.75300619118631</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B11" t="n">
-        <v>5.247560427873244</v>
+        <v>19.08091398635481</v>
       </c>
       <c r="C11" t="n">
-        <v>37.41786490059109</v>
+        <v>32.98056014766524</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B12" t="n">
-        <v>4.599086440615774</v>
+        <v>5.247560427873244</v>
       </c>
       <c r="C12" t="n">
-        <v>10.0372028702417</v>
+        <v>37.41786490059109</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B13" t="n">
-        <v>4.350545889754165</v>
+        <v>4.599086440615774</v>
       </c>
       <c r="C13" t="n">
-        <v>4.703456714920939</v>
+        <v>10.0372028702417</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B14" t="n">
-        <v>12.3154471376091</v>
+        <v>4.350545889754165</v>
       </c>
       <c r="C14" t="n">
-        <v>19.80102582373344</v>
+        <v>4.703456714920939</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B15" t="n">
-        <v>3.819950737498878</v>
+        <v>12.3154471376091</v>
       </c>
       <c r="C15" t="n">
-        <v>6.24883087916388</v>
+        <v>19.80102582373344</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B16" t="n">
-        <v>2.762844284902344</v>
+        <v>3.819950737498878</v>
       </c>
       <c r="C16" t="n">
-        <v>4.323216797503804</v>
+        <v>6.24883087916388</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B17" t="n">
-        <v>0.6290099552611617</v>
+        <v>2.762844284902344</v>
       </c>
       <c r="C17" t="n">
-        <v>8.606256362377396</v>
+        <v>4.323216797503804</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5057548924013222</v>
+        <v>0.6290099552611617</v>
       </c>
       <c r="C18" t="n">
-        <v>2.979694003164512</v>
+        <v>8.606256362377396</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B19" t="n">
-        <v>6.647778360750189</v>
+        <v>0.5057548924013222</v>
       </c>
       <c r="C19" t="n">
-        <v>-6.127044898596667</v>
+        <v>2.979694003164512</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B20" t="n">
-        <v>4.303804857467131</v>
+        <v>6.647778360750189</v>
       </c>
       <c r="C20" t="n">
-        <v>7.89299078256791</v>
+        <v>-6.127044898596667</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B21" t="n">
-        <v>2.924140980781398</v>
+        <v>4.303804857467131</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.2316081269587822</v>
+        <v>7.89299078256791</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B22" t="n">
-        <v>7.785935057409143</v>
+        <v>2.924140980781398</v>
       </c>
       <c r="C22" t="n">
-        <v>8.288539990171895</v>
+        <v>-0.2316081269587822</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.3110974876163297</v>
+        <v>7.785935057409143</v>
       </c>
       <c r="C23" t="n">
-        <v>-3.670035526014814</v>
+        <v>8.288539990171895</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B24" t="n">
-        <v>-3.930061753406378</v>
+        <v>-0.3110974876163297</v>
       </c>
       <c r="C24" t="n">
-        <v>-7.79675266346972</v>
+        <v>-3.670035526014814</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B25" t="n">
-        <v>5.302909476542483</v>
+        <v>-3.930061753406378</v>
       </c>
       <c r="C25" t="n">
-        <v>7.076324014940227</v>
+        <v>-7.79675266346972</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B26" t="n">
-        <v>4.764258814569922</v>
+        <v>5.302909476542483</v>
       </c>
       <c r="C26" t="n">
-        <v>5.982907474372823</v>
+        <v>7.076324014940227</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B27" t="n">
-        <v>3.374232331184368</v>
+        <v>4.764258814569922</v>
       </c>
       <c r="C27" t="n">
-        <v>1.502936720396852</v>
+        <v>5.982907474372823</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B28" t="n">
-        <v>-3.216230791005115</v>
+        <v>3.374232331184368</v>
       </c>
       <c r="C28" t="n">
-        <v>-4.726432032443128</v>
+        <v>1.502936720396852</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B29" t="n">
-        <v>-1.076847507836964</v>
+        <v>-3.216230791005115</v>
       </c>
       <c r="C29" t="n">
-        <v>-5.187634688078601</v>
+        <v>-4.726432032443128</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B30" t="n">
-        <v>0.6734557165223753</v>
+        <v>-1.076847507836964</v>
       </c>
       <c r="C30" t="n">
-        <v>15.32586722211562</v>
+        <v>-5.187634688078601</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B31" t="n">
-        <v>7.54283768190398</v>
+        <v>0.6734557165223753</v>
       </c>
       <c r="C31" t="n">
-        <v>8.4783202773973</v>
+        <v>15.32586722211562</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B32" t="n">
-        <v>7.25654020393236</v>
+        <v>7.54283768190398</v>
       </c>
       <c r="C32" t="n">
-        <v>6.047733486673468</v>
+        <v>8.4783202773973</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B33" t="n">
-        <v>-1.068415578494741</v>
+        <v>7.25654020393236</v>
       </c>
       <c r="C33" t="n">
-        <v>-3.258245561246353</v>
+        <v>6.047733486673468</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.5777140778466916</v>
+        <v>-1.068415578494741</v>
       </c>
       <c r="C34" t="n">
-        <v>-2.202831754727963</v>
+        <v>-3.258245561246353</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B35" t="n">
-        <v>0.9595452622609635</v>
+        <v>-0.5777140778466916</v>
       </c>
       <c r="C35" t="n">
-        <v>-3.256936449935688</v>
+        <v>-2.202831754727963</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B36" t="n">
-        <v>2.093738232490927</v>
+        <v>0.9595452622609635</v>
       </c>
       <c r="C36" t="n">
-        <v>5.025337343490821</v>
+        <v>-3.256936449935688</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B37" t="n">
-        <v>5.619802001040464</v>
+        <v>2.093738232490927</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6802768899403677</v>
+        <v>5.025337343490821</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B38" t="n">
-        <v>-2.105258372825114</v>
+        <v>5.619802001040464</v>
       </c>
       <c r="C38" t="n">
-        <v>-3.724932900574174</v>
+        <v>0.6802768899403677</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.6119253340401531</v>
+        <v>-2.105258372825114</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8392963783575125</v>
+        <v>-3.724932900574174</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B40" t="n">
-        <v>2.737778212377684</v>
+        <v>-0.6119253340401531</v>
       </c>
       <c r="C40" t="n">
-        <v>7.562528686444536</v>
+        <v>0.8392963783575125</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B41" t="n">
-        <v>-3.559553406618587</v>
+        <v>2.737778212377684</v>
       </c>
       <c r="C41" t="n">
-        <v>-3.71900911798525</v>
+        <v>7.562528686444536</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.234144257336133</v>
+        <v>-3.559553406618587</v>
       </c>
       <c r="C42" t="n">
-        <v>-3.968255956784306</v>
+        <v>-3.71900911798525</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B43" t="n">
-        <v>0.3524580110659814</v>
+        <v>-0.234144257336133</v>
       </c>
       <c r="C43" t="n">
-        <v>3.410221769566157</v>
+        <v>-3.968255956784306</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B44" t="n">
-        <v>7.719890021497</v>
+        <v>0.3524580110659814</v>
       </c>
       <c r="C44" t="n">
-        <v>13.10819252034816</v>
+        <v>3.410221769566157</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B45" t="n">
-        <v>-2.588860425183181</v>
+        <v>7.719890021497</v>
       </c>
       <c r="C45" t="n">
-        <v>-6.718428768534002</v>
+        <v>13.10819252034816</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B46" t="n">
-        <v>4.01794660532715</v>
+        <v>-2.588860425183181</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.3718577830090442</v>
+        <v>-6.718428768534002</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B47" t="n">
-        <v>3.747233921473403</v>
+        <v>4.01794660532715</v>
       </c>
       <c r="C47" t="n">
-        <v>9.63797079504587</v>
+        <v>-0.3718577830090442</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B48" t="n">
-        <v>4.325697320578858</v>
+        <v>3.747233921473403</v>
       </c>
       <c r="C48" t="n">
-        <v>7.371737067902551</v>
+        <v>9.63797079504587</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1621865038732517</v>
+        <v>4.325697320578858</v>
       </c>
       <c r="C49" t="n">
-        <v>1.764080002332857</v>
+        <v>7.371737067902551</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B50" t="n">
-        <v>-1.685652967530238</v>
+        <v>0.1621865038732517</v>
       </c>
       <c r="C50" t="n">
-        <v>3.237671636813877</v>
+        <v>1.764080002332857</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.3631408134932568</v>
+        <v>-1.685652967530238</v>
       </c>
       <c r="C51" t="n">
-        <v>-5.296168701592718</v>
+        <v>3.237671636813877</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B52" t="n">
-        <v>0.6855645869853433</v>
+        <v>-0.3631408134932568</v>
       </c>
       <c r="C52" t="n">
-        <v>-2.662370124342184</v>
+        <v>-5.296168701592718</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.4323149900067103</v>
+        <v>0.6855645869853433</v>
       </c>
       <c r="C53" t="n">
-        <v>-3.848036099611796</v>
+        <v>-2.662370124342184</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B54" t="n">
-        <v>-1.875418922567351</v>
+        <v>-0.4323149900067103</v>
       </c>
       <c r="C54" t="n">
-        <v>-5.017806843863504</v>
+        <v>-3.848036099611796</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B55" t="n">
-        <v>1.518590208211412</v>
+        <v>-1.875418922567351</v>
       </c>
       <c r="C55" t="n">
-        <v>-2.609356376021654</v>
+        <v>-5.017806843863504</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B56" t="n">
-        <v>1.215872396057804</v>
+        <v>1.518590208211412</v>
       </c>
       <c r="C56" t="n">
-        <v>2.235936178495601</v>
+        <v>-2.609356376021654</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B57" t="n">
-        <v>5.67272764263731</v>
+        <v>1.215872396057804</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2.235936178495601</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
+        <v>44620</v>
+      </c>
+      <c r="B58" t="n">
+        <v>5.67272764263731</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
         <v>44592</v>
       </c>
     </row>
@@ -13980,7 +14013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14002,204 +14035,215 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46295</v>
+        <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>4.846076621567041</v>
+        <v>-0.1315865100202984</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.503623765107864</v>
+        <v>-0.4341133596590274</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="B3" t="n">
-        <v>-4.307287000201954</v>
+        <v>4.846076621567041</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.508697926328606</v>
+        <v>-1.503623765107864</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="B4" t="n">
-        <v>10.06266621527294</v>
+        <v>-4.307287000201954</v>
       </c>
       <c r="C4" t="n">
-        <v>0.301726397146429</v>
+        <v>-1.508697926328606</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46022</v>
+        <v>46112</v>
       </c>
       <c r="B5" t="n">
-        <v>14.87741508945415</v>
+        <v>10.06266621527294</v>
       </c>
       <c r="C5" t="n">
-        <v>58.32290812072105</v>
+        <v>0.301726397146429</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45930</v>
+        <v>46022</v>
       </c>
       <c r="B6" t="n">
-        <v>19.82747972735621</v>
+        <v>14.87741508945415</v>
       </c>
       <c r="C6" t="n">
-        <v>32.79009046866983</v>
+        <v>58.32290812072105</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45838</v>
+        <v>45930</v>
       </c>
       <c r="B7" t="n">
-        <v>7.861372591380933</v>
+        <v>19.82747972735621</v>
       </c>
       <c r="C7" t="n">
-        <v>4.989756990491467</v>
+        <v>32.79009046866983</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45747</v>
+        <v>45838</v>
       </c>
       <c r="B8" t="n">
-        <v>15.71229193262609</v>
+        <v>7.861372591380933</v>
       </c>
       <c r="C8" t="n">
-        <v>16.56514339078781</v>
+        <v>4.989756990491467</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45657</v>
+        <v>45747</v>
       </c>
       <c r="B9" t="n">
-        <v>0.8497200744499223</v>
+        <v>15.71229193262609</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.895499220552157</v>
+        <v>16.56514339078781</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45565</v>
+        <v>45657</v>
       </c>
       <c r="B10" t="n">
-        <v>4.816094536539461</v>
+        <v>0.8497200744499223</v>
       </c>
       <c r="C10" t="n">
-        <v>2.49126816255496</v>
+        <v>-4.895499220552157</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45473</v>
+        <v>45565</v>
       </c>
       <c r="B11" t="n">
-        <v>7.101219597988462</v>
+        <v>4.816094536539461</v>
       </c>
       <c r="C11" t="n">
-        <v>18.613647746147</v>
+        <v>2.49126816255496</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45382</v>
+        <v>45473</v>
       </c>
       <c r="B12" t="n">
-        <v>5.497578776235734</v>
+        <v>7.101219597988462</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3324991171443914</v>
+        <v>18.613647746147</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45291</v>
+        <v>45382</v>
       </c>
       <c r="B13" t="n">
-        <v>8.865893387533141</v>
+        <v>5.497578776235734</v>
       </c>
       <c r="C13" t="n">
-        <v>2.295922339335066</v>
+        <v>0.3324991171443914</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45199</v>
+        <v>45291</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.04056065140266574</v>
+        <v>8.865893387533141</v>
       </c>
       <c r="C14" t="n">
-        <v>4.425037557012979</v>
+        <v>2.295922339335066</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45107</v>
+        <v>45199</v>
       </c>
       <c r="B15" t="n">
-        <v>-3.446246978755263</v>
+        <v>-0.04056065140266574</v>
       </c>
       <c r="C15" t="n">
-        <v>-4.38658349291331</v>
+        <v>4.425037557012979</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45016</v>
+        <v>45107</v>
       </c>
       <c r="B16" t="n">
-        <v>9.147250898805925</v>
+        <v>-3.446246978755263</v>
       </c>
       <c r="C16" t="n">
-        <v>5.116755377429172</v>
+        <v>-4.38658349291331</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>44926</v>
+        <v>45016</v>
       </c>
       <c r="B17" t="n">
-        <v>8.41056784279135</v>
+        <v>9.147250898805925</v>
       </c>
       <c r="C17" t="n">
-        <v>19.79687212491488</v>
+        <v>5.116755377429172</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>44834</v>
+        <v>44926</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.371111739339004</v>
+        <v>8.41056784279135</v>
       </c>
       <c r="C18" t="n">
-        <v>-4.832969696154221</v>
+        <v>19.79687212491488</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>44742</v>
+        <v>44834</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.8159578854644911</v>
+        <v>-1.371111739339004</v>
       </c>
       <c r="C19" t="n">
-        <v>-11.05580919103796</v>
+        <v>-4.832969696154221</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
+        <v>44742</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.8159578854644911</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-11.05580919103796</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
         <v>44651</v>
       </c>
     </row>
@@ -14226,7 +14270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C902"/>
+  <dimension ref="A1:C904"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24155,6 +24199,28 @@
       </c>
       <c r="C902" t="n">
         <v>57.59717598245165</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B903" t="n">
+        <v>26.62147901260203</v>
+      </c>
+      <c r="C903" t="n">
+        <v>50.08630114920432</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B904" t="n">
+        <v>26.68753493820986</v>
+      </c>
+      <c r="C904" t="n">
+        <v>53.38428417701675</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1179"/>
+  <dimension ref="A1:C1180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13328,6 +13328,17 @@
       </c>
       <c r="C1179" t="n">
         <v>208.7100067138672</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1180" t="n">
+        <v>121.5800018310547</v>
+      </c>
+      <c r="C1180" t="n">
+        <v>211.8500061035156</v>
       </c>
     </row>
   </sheetData>
@@ -13366,10 +13377,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1315865100202984</v>
+        <v>-0.008219843027357232</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4341133596590274</v>
+        <v>1.063835053083295</v>
       </c>
     </row>
     <row r="3">
@@ -14038,10 +14049,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1315865100202984</v>
+        <v>-0.008219843027357232</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4341133596590274</v>
+        <v>1.063835053083295</v>
       </c>
     </row>
     <row r="3">
@@ -14270,7 +14281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C904"/>
+  <dimension ref="A1:C905"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24221,6 +24232,17 @@
       </c>
       <c r="C904" t="n">
         <v>53.38428417701675</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B905" t="n">
+        <v>24.53139941760907</v>
+      </c>
+      <c r="C905" t="n">
+        <v>51.46208157512338</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13335,10 +13335,10 @@
         <v>46300</v>
       </c>
       <c r="B1180" t="n">
-        <v>121.5800018310547</v>
+        <v>121.4300003051758</v>
       </c>
       <c r="C1180" t="n">
-        <v>211.8500061035156</v>
+        <v>208.7100067138672</v>
       </c>
     </row>
   </sheetData>
@@ -13377,10 +13377,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.008219843027357232</v>
+        <v>-0.1315865100202984</v>
       </c>
       <c r="C2" t="n">
-        <v>1.063835053083295</v>
+        <v>-0.4341133596590274</v>
       </c>
     </row>
     <row r="3">
@@ -14049,10 +14049,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.008219843027357232</v>
+        <v>-0.1315865100202984</v>
       </c>
       <c r="C2" t="n">
-        <v>1.063835053083295</v>
+        <v>-0.4341133596590274</v>
       </c>
     </row>
     <row r="3">
@@ -24239,10 +24239,10 @@
         <v>46300</v>
       </c>
       <c r="B905" t="n">
-        <v>24.53139941760907</v>
+        <v>24.37775655158547</v>
       </c>
       <c r="C905" t="n">
-        <v>51.46208157512338</v>
+        <v>49.21714020151595</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13332,13 +13332,13 @@
     </row>
     <row r="1180">
       <c r="A1180" s="2" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B1180" t="n">
-        <v>121.4300003051758</v>
+        <v>121.4599990844727</v>
       </c>
       <c r="C1180" t="n">
-        <v>208.7100067138672</v>
+        <v>210.6999969482422</v>
       </c>
     </row>
   </sheetData>
@@ -13377,10 +13377,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1315865100202984</v>
+        <v>-0.1069144315595794</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4341133596590274</v>
+        <v>0.5152188990610984</v>
       </c>
     </row>
     <row r="3">
@@ -14049,10 +14049,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1315865100202984</v>
+        <v>-0.1069144315595794</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4341133596590274</v>
+        <v>0.5152188990610984</v>
       </c>
     </row>
     <row r="3">
@@ -24236,13 +24236,13 @@
     </row>
     <row r="905">
       <c r="A905" s="2" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B905" t="n">
-        <v>24.37775655158547</v>
+        <v>24.40848356187002</v>
       </c>
       <c r="C905" t="n">
-        <v>49.21714020151595</v>
+        <v>50.63988296540018</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13335,10 +13335,10 @@
         <v>46301</v>
       </c>
       <c r="B1180" t="n">
-        <v>121.4599990844727</v>
+        <v>121.4300003051758</v>
       </c>
       <c r="C1180" t="n">
-        <v>210.6999969482422</v>
+        <v>208.7100067138672</v>
       </c>
     </row>
   </sheetData>
@@ -13377,10 +13377,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1069144315595794</v>
+        <v>-0.1315865100202984</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5152188990610984</v>
+        <v>-0.4341133596590274</v>
       </c>
     </row>
     <row r="3">
@@ -14049,10 +14049,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1069144315595794</v>
+        <v>-0.1315865100202984</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5152188990610984</v>
+        <v>-0.4341133596590274</v>
       </c>
     </row>
     <row r="3">
@@ -24239,10 +24239,10 @@
         <v>46301</v>
       </c>
       <c r="B905" t="n">
-        <v>24.40848356187002</v>
+        <v>24.37775655158547</v>
       </c>
       <c r="C905" t="n">
-        <v>50.63988296540018</v>
+        <v>49.21714020151595</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1180"/>
+  <dimension ref="A1:C1181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13332,13 +13332,24 @@
     </row>
     <row r="1180">
       <c r="A1180" s="2" t="n">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="B1180" t="n">
-        <v>121.4300003051758</v>
+        <v>121.5800018310547</v>
       </c>
       <c r="C1180" t="n">
-        <v>208.7100067138672</v>
+        <v>211.8500061035156</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1181" t="n">
+        <v>121.0800018310547</v>
+      </c>
+      <c r="C1181" t="n">
+        <v>209.0200042724609</v>
       </c>
     </row>
   </sheetData>
@@ -13377,10 +13388,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1315865100202984</v>
+        <v>-0.4194378832109602</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4341133596590274</v>
+        <v>-0.2862278688591458</v>
       </c>
     </row>
     <row r="3">
@@ -14049,10 +14060,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1315865100202984</v>
+        <v>-0.4194378832109602</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4341133596590274</v>
+        <v>-0.2862278688591458</v>
       </c>
     </row>
     <row r="3">
@@ -14281,7 +14292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C905"/>
+  <dimension ref="A1:C906"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24236,13 +24247,24 @@
     </row>
     <row r="905">
       <c r="A905" s="2" t="n">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="B905" t="n">
-        <v>24.37775655158547</v>
+        <v>24.53139941760907</v>
       </c>
       <c r="C905" t="n">
-        <v>49.21714020151595</v>
+        <v>51.46208157512338</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B906" t="n">
+        <v>24.73472979469957</v>
+      </c>
+      <c r="C906" t="n">
+        <v>49.55639130497915</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13346,10 +13346,10 @@
         <v>46302</v>
       </c>
       <c r="B1181" t="n">
-        <v>121.0800018310547</v>
+        <v>121.5800018310547</v>
       </c>
       <c r="C1181" t="n">
-        <v>209.0200042724609</v>
+        <v>211.8500061035156</v>
       </c>
     </row>
   </sheetData>
@@ -13388,10 +13388,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.4194378832109602</v>
+        <v>-0.008219843027357232</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2862278688591458</v>
+        <v>1.063835053083295</v>
       </c>
     </row>
     <row r="3">
@@ -14060,10 +14060,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.4194378832109602</v>
+        <v>-0.008219843027357232</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2862278688591458</v>
+        <v>1.063835053083295</v>
       </c>
     </row>
     <row r="3">
@@ -24261,10 +24261,10 @@
         <v>46302</v>
       </c>
       <c r="B906" t="n">
-        <v>24.73472979469957</v>
+        <v>25.24982199782302</v>
       </c>
       <c r="C906" t="n">
-        <v>49.55639130497915</v>
+        <v>51.58129252298562</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1181"/>
+  <dimension ref="A1:C1182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13343,13 +13343,24 @@
     </row>
     <row r="1181">
       <c r="A1181" s="2" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="B1181" t="n">
-        <v>121.5800018310547</v>
+        <v>121.4599990844727</v>
       </c>
       <c r="C1181" t="n">
-        <v>211.8500061035156</v>
+        <v>210.6999969482422</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1182" t="n">
+        <v>120.9400024414062</v>
+      </c>
+      <c r="C1182" t="n">
+        <v>205.8699951171875</v>
       </c>
     </row>
   </sheetData>
@@ -13388,10 +13399,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.008219843027357232</v>
+        <v>-0.5345784324872316</v>
       </c>
       <c r="C2" t="n">
-        <v>1.063835053083295</v>
+        <v>-1.788951477602874</v>
       </c>
     </row>
     <row r="3">
@@ -14060,10 +14071,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.008219843027357232</v>
+        <v>-0.5345784324872316</v>
       </c>
       <c r="C2" t="n">
-        <v>1.063835053083295</v>
+        <v>-1.788951477602874</v>
       </c>
     </row>
     <row r="3">
@@ -14292,7 +14303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C906"/>
+  <dimension ref="A1:C907"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24258,13 +24269,24 @@
     </row>
     <row r="906">
       <c r="A906" s="2" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="B906" t="n">
-        <v>25.24982199782302</v>
+        <v>25.12619703958743</v>
       </c>
       <c r="C906" t="n">
-        <v>51.58129252298562</v>
+        <v>50.75844678710004</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B907" t="n">
+        <v>21.89074879407586</v>
+      </c>
+      <c r="C907" t="n">
+        <v>43.29365750746346</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13357,10 +13357,10 @@
         <v>46303</v>
       </c>
       <c r="B1182" t="n">
-        <v>120.9400024414062</v>
+        <v>121.4599990844727</v>
       </c>
       <c r="C1182" t="n">
-        <v>205.8699951171875</v>
+        <v>210.6999969482422</v>
       </c>
     </row>
   </sheetData>
@@ -13399,10 +13399,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.5345784324872316</v>
+        <v>-0.1069144315595794</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.788951477602874</v>
+        <v>0.5152188990610984</v>
       </c>
     </row>
     <row r="3">
@@ -14071,10 +14071,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.5345784324872316</v>
+        <v>-0.1069144315595794</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.788951477602874</v>
+        <v>0.5152188990610984</v>
       </c>
     </row>
     <row r="3">
@@ -24283,10 +24283,10 @@
         <v>46303</v>
       </c>
       <c r="B907" t="n">
-        <v>21.89074879407586</v>
+        <v>22.41483328981149</v>
       </c>
       <c r="C907" t="n">
-        <v>43.29365750746346</v>
+        <v>46.6555297790667</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1182"/>
+  <dimension ref="A1:C1178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12111,1256 +12111,1212 @@
     </row>
     <row r="1069">
       <c r="A1069" s="2" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B1069" t="n">
-        <v>123.4300003051758</v>
+        <v>122.379997253418</v>
       </c>
       <c r="C1069" t="n">
-        <v>227.5</v>
+        <v>230.3600006103516</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" s="2" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1070" t="n">
-        <v>122.379997253418</v>
+        <v>122.1600036621094</v>
       </c>
       <c r="C1070" t="n">
-        <v>230.3600006103516</v>
+        <v>228.8899993896484</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" s="2" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1071" t="n">
-        <v>122.1600036621094</v>
+        <v>124.0199966430664</v>
       </c>
       <c r="C1071" t="n">
-        <v>228.8899993896484</v>
+        <v>234.4900054931641</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" s="2" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1072" t="n">
-        <v>124.0199966430664</v>
+        <v>124.4700012207031</v>
       </c>
       <c r="C1072" t="n">
-        <v>234.4900054931641</v>
+        <v>239.4400024414062</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" s="2" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1073" t="n">
-        <v>124.4700012207031</v>
+        <v>124.3099975585938</v>
       </c>
       <c r="C1073" t="n">
-        <v>239.4400024414062</v>
+        <v>240.1699981689453</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" s="2" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B1074" t="n">
-        <v>124.3099975585938</v>
+        <v>123.2300033569336</v>
       </c>
       <c r="C1074" t="n">
-        <v>240.1699981689453</v>
+        <v>241.2899932861328</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" s="2" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1075" t="n">
-        <v>123.2300033569336</v>
+        <v>124.6100006103516</v>
       </c>
       <c r="C1075" t="n">
-        <v>241.2899932861328</v>
+        <v>252.0099945068359</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" s="2" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1076" t="n">
-        <v>124.6100006103516</v>
+        <v>131.7400054931641</v>
       </c>
       <c r="C1076" t="n">
-        <v>252.0099945068359</v>
+        <v>269.4200134277344</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" s="2" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1077" t="n">
-        <v>131.7400054931641</v>
+        <v>131.7799987792969</v>
       </c>
       <c r="C1077" t="n">
-        <v>269.4200134277344</v>
+        <v>270.9299926757812</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" s="2" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1078" t="n">
-        <v>131.7799987792969</v>
+        <v>129.4100036621094</v>
       </c>
       <c r="C1078" t="n">
-        <v>270.9299926757812</v>
+        <v>249.8500061035156</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" s="2" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B1079" t="n">
-        <v>129.4100036621094</v>
+        <v>129.6999969482422</v>
       </c>
       <c r="C1079" t="n">
-        <v>249.8500061035156</v>
+        <v>253.1600036621094</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" s="2" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1080" t="n">
-        <v>129.6999969482422</v>
+        <v>130.6399993896484</v>
       </c>
       <c r="C1080" t="n">
-        <v>253.1600036621094</v>
+        <v>253.25</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" s="2" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1081" t="n">
-        <v>130.6399993896484</v>
+        <v>130.1999969482422</v>
       </c>
       <c r="C1081" t="n">
-        <v>253.25</v>
+        <v>252.6600036621094</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" s="2" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1082" t="n">
-        <v>130.1999969482422</v>
+        <v>130.7400054931641</v>
       </c>
       <c r="C1082" t="n">
-        <v>252.6600036621094</v>
+        <v>251.9700012207031</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" s="2" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1083" t="n">
-        <v>130.7400054931641</v>
+        <v>130.5</v>
       </c>
       <c r="C1083" t="n">
-        <v>251.9700012207031</v>
+        <v>252.5399932861328</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" s="2" t="n">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B1084" t="n">
-        <v>130.5</v>
+        <v>130.5099945068359</v>
       </c>
       <c r="C1084" t="n">
-        <v>252.5399932861328</v>
+        <v>256.0299987792969</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" s="2" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1085" t="n">
-        <v>130.5099945068359</v>
+        <v>129.5800018310547</v>
       </c>
       <c r="C1085" t="n">
-        <v>256.0299987792969</v>
+        <v>251.2899932861328</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" s="2" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1086" t="n">
-        <v>129.5800018310547</v>
+        <v>129.0399932861328</v>
       </c>
       <c r="C1086" t="n">
-        <v>251.2899932861328</v>
+        <v>249.8699951171875</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" s="2" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B1087" t="n">
-        <v>129.0399932861328</v>
+        <v>128.6499938964844</v>
       </c>
       <c r="C1087" t="n">
-        <v>249.8699951171875</v>
+        <v>249.3699951171875</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" s="2" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B1088" t="n">
-        <v>129.0399932861328</v>
+        <v>127.4899978637695</v>
       </c>
       <c r="C1088" t="n">
-        <v>249.8699951171875</v>
+        <v>249.5399932861328</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" s="2" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B1089" t="n">
-        <v>128.6499938964844</v>
+        <v>128.6699981689453</v>
       </c>
       <c r="C1089" t="n">
-        <v>249.3699951171875</v>
+        <v>251.5599975585938</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" s="2" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B1090" t="n">
-        <v>127.4899978637695</v>
+        <v>127.6399993896484</v>
       </c>
       <c r="C1090" t="n">
-        <v>249.5399932861328</v>
+        <v>246.7899932861328</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" s="2" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B1091" t="n">
-        <v>128.6699981689453</v>
+        <v>128.5</v>
       </c>
       <c r="C1091" t="n">
-        <v>251.5599975585938</v>
+        <v>246.5599975585938</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" s="2" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B1092" t="n">
-        <v>127.6399993896484</v>
+        <v>127.7799987792969</v>
       </c>
       <c r="C1092" t="n">
-        <v>246.7899932861328</v>
+        <v>243.5800018310547</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" s="2" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B1093" t="n">
-        <v>128.5</v>
+        <v>124.1600036621094</v>
       </c>
       <c r="C1093" t="n">
-        <v>246.5599975585938</v>
+        <v>227.9299926757812</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" s="2" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B1094" t="n">
-        <v>127.7799987792969</v>
+        <v>125.3899993896484</v>
       </c>
       <c r="C1094" t="n">
-        <v>243.5800018310547</v>
+        <v>231.8999938964844</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" s="2" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B1095" t="n">
-        <v>124.1600036621094</v>
+        <v>121.1500015258789</v>
       </c>
       <c r="C1095" t="n">
-        <v>227.9299926757812</v>
+        <v>220.5899963378906</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" s="2" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B1096" t="n">
-        <v>125.3899993896484</v>
+        <v>119.2799987792969</v>
       </c>
       <c r="C1096" t="n">
-        <v>231.8999938964844</v>
+        <v>221.3800048828125</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" s="2" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B1097" t="n">
-        <v>121.1500015258789</v>
+        <v>121.9199981689453</v>
       </c>
       <c r="C1097" t="n">
-        <v>220.5899963378906</v>
+        <v>229.7599945068359</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" s="2" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B1098" t="n">
-        <v>119.2799987792969</v>
+        <v>124.1100006103516</v>
       </c>
       <c r="C1098" t="n">
-        <v>221.3800048828125</v>
+        <v>238.6199951171875</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" s="2" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B1099" t="n">
-        <v>121.9199981689453</v>
+        <v>124.1399993896484</v>
       </c>
       <c r="C1099" t="n">
-        <v>229.7599945068359</v>
+        <v>236.1300048828125</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" s="2" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B1100" t="n">
-        <v>124.1100006103516</v>
+        <v>123.75</v>
       </c>
       <c r="C1100" t="n">
-        <v>238.6199951171875</v>
+        <v>234.6699981689453</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" s="2" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B1101" t="n">
-        <v>124.1399993896484</v>
+        <v>122.120002746582</v>
       </c>
       <c r="C1101" t="n">
-        <v>236.1300048828125</v>
+        <v>229.9900054931641</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" s="2" t="n">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="B1102" t="n">
-        <v>123.75</v>
+        <v>119.7900009155273</v>
       </c>
       <c r="C1102" t="n">
-        <v>234.6699981689453</v>
+        <v>221.4199981689453</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" s="2" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B1103" t="n">
-        <v>122.120002746582</v>
+        <v>121.120002746582</v>
       </c>
       <c r="C1103" t="n">
-        <v>229.9900054931641</v>
+        <v>225.1399993896484</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" s="2" t="n">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="B1104" t="n">
-        <v>119.7900009155273</v>
+        <v>118.9000015258789</v>
       </c>
       <c r="C1104" t="n">
-        <v>221.4199981689453</v>
+        <v>215.0599975585938</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" s="2" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B1105" t="n">
-        <v>121.120002746582</v>
+        <v>117.5599975585938</v>
       </c>
       <c r="C1105" t="n">
-        <v>225.1399993896484</v>
+        <v>213.3500061035156</v>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" s="2" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B1106" t="n">
-        <v>118.9000015258789</v>
+        <v>114.9599990844727</v>
       </c>
       <c r="C1106" t="n">
-        <v>215.0599975585938</v>
+        <v>206.5700073242188</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" s="2" t="n">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="B1107" t="n">
-        <v>117.5599975585938</v>
+        <v>116.4300003051758</v>
       </c>
       <c r="C1107" t="n">
-        <v>213.3500061035156</v>
+        <v>208.0200042724609</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" s="2" t="n">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="B1108" t="n">
-        <v>114.9599990844727</v>
+        <v>115.9700012207031</v>
       </c>
       <c r="C1108" t="n">
-        <v>206.5700073242188</v>
+        <v>212.8200073242188</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" s="2" t="n">
-        <v>46199</v>
+        <v>46204</v>
       </c>
       <c r="B1109" t="n">
-        <v>114.9599990844727</v>
+        <v>115.4599990844727</v>
       </c>
       <c r="C1109" t="n">
-        <v>206.5700073242188</v>
+        <v>211.3399963378906</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" s="2" t="n">
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="B1110" t="n">
-        <v>116.4300003051758</v>
+        <v>117.6900024414062</v>
       </c>
       <c r="C1110" t="n">
-        <v>208.0200042724609</v>
+        <v>216.2799987792969</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" s="2" t="n">
-        <v>46203</v>
+        <v>46206</v>
       </c>
       <c r="B1111" t="n">
-        <v>115.9700012207031</v>
+        <v>120.3099975585938</v>
       </c>
       <c r="C1111" t="n">
-        <v>212.8200073242188</v>
+        <v>221.3099975585938</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" s="2" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B1112" t="n">
-        <v>115.4599990844727</v>
+        <v>119.5100021362305</v>
       </c>
       <c r="C1112" t="n">
-        <v>211.3399963378906</v>
+        <v>220.3600006103516</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" s="2" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B1113" t="n">
-        <v>117.6900024414062</v>
+        <v>118.5800018310547</v>
       </c>
       <c r="C1113" t="n">
-        <v>216.2799987792969</v>
+        <v>216.2899932861328</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" s="2" t="n">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="B1114" t="n">
-        <v>120.3099975585938</v>
+        <v>116.9599990844727</v>
       </c>
       <c r="C1114" t="n">
-        <v>221.3099975585938</v>
+        <v>210.1499938964844</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" s="2" t="n">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="B1115" t="n">
-        <v>119.5100021362305</v>
+        <v>118.4199981689453</v>
       </c>
       <c r="C1115" t="n">
-        <v>220.3600006103516</v>
+        <v>212.9499969482422</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" s="2" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="B1116" t="n">
-        <v>118.5800018310547</v>
+        <v>118.1399993896484</v>
       </c>
       <c r="C1116" t="n">
-        <v>216.2899932861328</v>
+        <v>208.8300018310547</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" s="2" t="n">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="B1117" t="n">
-        <v>116.9599990844727</v>
+        <v>116.9499969482422</v>
       </c>
       <c r="C1117" t="n">
-        <v>210.1499938964844</v>
+        <v>207.4600067138672</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" s="2" t="n">
-        <v>46212</v>
+        <v>46217</v>
       </c>
       <c r="B1118" t="n">
-        <v>118.4199981689453</v>
+        <v>115.9800033569336</v>
       </c>
       <c r="C1118" t="n">
-        <v>212.9499969482422</v>
+        <v>208.0099945068359</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" s="2" t="n">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="B1119" t="n">
-        <v>118.1399993896484</v>
+        <v>116.3899993896484</v>
       </c>
       <c r="C1119" t="n">
-        <v>208.8300018310547</v>
+        <v>208.6600036621094</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" s="2" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="B1120" t="n">
-        <v>116.9499969482422</v>
+        <v>116.4700012207031</v>
       </c>
       <c r="C1120" t="n">
-        <v>207.4600067138672</v>
+        <v>206.8399963378906</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" s="2" t="n">
-        <v>46217</v>
+        <v>46220</v>
       </c>
       <c r="B1121" t="n">
-        <v>115.9800033569336</v>
+        <v>115.7900009155273</v>
       </c>
       <c r="C1121" t="n">
-        <v>208.0099945068359</v>
+        <v>204.9199981689453</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" s="2" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="B1122" t="n">
-        <v>116.3899993896484</v>
+        <v>116.8399963378906</v>
       </c>
       <c r="C1122" t="n">
-        <v>208.6600036621094</v>
+        <v>207.8899993896484</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" s="2" t="n">
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="B1123" t="n">
-        <v>116.4700012207031</v>
+        <v>117.7300033569336</v>
       </c>
       <c r="C1123" t="n">
-        <v>206.8399963378906</v>
+        <v>212.2299957275391</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" s="2" t="n">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="B1124" t="n">
-        <v>115.7900009155273</v>
+        <v>119.1399993896484</v>
       </c>
       <c r="C1124" t="n">
-        <v>204.9199981689453</v>
+        <v>213.0700073242188</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" s="2" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B1125" t="n">
-        <v>116.8399963378906</v>
+        <v>118.6900024414062</v>
       </c>
       <c r="C1125" t="n">
-        <v>207.8899993896484</v>
+        <v>211</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" s="2" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="B1126" t="n">
-        <v>117.7300033569336</v>
+        <v>117.9100036621094</v>
       </c>
       <c r="C1126" t="n">
-        <v>212.2299957275391</v>
+        <v>210.9600067138672</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" s="2" t="n">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="B1127" t="n">
-        <v>119.1399993896484</v>
+        <v>118.620002746582</v>
       </c>
       <c r="C1127" t="n">
-        <v>213.0700073242188</v>
+        <v>213.0099945068359</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" s="2" t="n">
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="B1128" t="n">
-        <v>118.6900024414062</v>
+        <v>116.8300018310547</v>
       </c>
       <c r="C1128" t="n">
-        <v>211</v>
+        <v>206.1999969482422</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" s="2" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="B1129" t="n">
-        <v>117.9100036621094</v>
+        <v>116.8499984741211</v>
       </c>
       <c r="C1129" t="n">
-        <v>210.9600067138672</v>
+        <v>206.6900024414062</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" s="2" t="n">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="B1130" t="n">
-        <v>118.620002746582</v>
+        <v>117.370002746582</v>
       </c>
       <c r="C1130" t="n">
-        <v>213.0099945068359</v>
+        <v>206.6300048828125</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" s="2" t="n">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="B1131" t="n">
-        <v>116.8300018310547</v>
+        <v>117.1100006103516</v>
       </c>
       <c r="C1131" t="n">
-        <v>206.1999969482422</v>
+        <v>206.5099945068359</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" s="2" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="B1132" t="n">
-        <v>116.8499984741211</v>
+        <v>117.2600021362305</v>
       </c>
       <c r="C1132" t="n">
-        <v>206.6900024414062</v>
+        <v>206.4499969482422</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" s="2" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="B1133" t="n">
-        <v>117.370002746582</v>
+        <v>117.1500015258789</v>
       </c>
       <c r="C1133" t="n">
-        <v>206.6300048828125</v>
+        <v>207.3500061035156</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" s="2" t="n">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="B1134" t="n">
-        <v>117.1100006103516</v>
+        <v>119.3899993896484</v>
       </c>
       <c r="C1134" t="n">
-        <v>206.5099945068359</v>
+        <v>213.3899993896484</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" s="2" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B1135" t="n">
-        <v>117.2600021362305</v>
+        <v>122.4800033569336</v>
       </c>
       <c r="C1135" t="n">
-        <v>206.4499969482422</v>
+        <v>214.5299987792969</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" s="2" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="B1136" t="n">
-        <v>117.1500015258789</v>
+        <v>123.4000015258789</v>
       </c>
       <c r="C1136" t="n">
-        <v>207.3500061035156</v>
+        <v>220.4700012207031</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" s="2" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B1137" t="n">
-        <v>119.3899993896484</v>
+        <v>124.5800018310547</v>
       </c>
       <c r="C1137" t="n">
-        <v>213.3899993896484</v>
+        <v>220.4600067138672</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" s="2" t="n">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="B1138" t="n">
-        <v>122.4800033569336</v>
+        <v>125.5199966430664</v>
       </c>
       <c r="C1138" t="n">
-        <v>214.5299987792969</v>
+        <v>222.3200073242188</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" s="2" t="n">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="B1139" t="n">
-        <v>123.4000015258789</v>
+        <v>126.4499969482422</v>
       </c>
       <c r="C1139" t="n">
-        <v>220.4700012207031</v>
+        <v>225.7599945068359</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" s="2" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="B1140" t="n">
-        <v>124.5800018310547</v>
+        <v>125.4800033569336</v>
       </c>
       <c r="C1140" t="n">
-        <v>220.4600067138672</v>
+        <v>220.9700012207031</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" s="2" t="n">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="B1141" t="n">
-        <v>125.5199966430664</v>
+        <v>125.129997253418</v>
       </c>
       <c r="C1141" t="n">
-        <v>222.3200073242188</v>
+        <v>221.2200012207031</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" s="2" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B1142" t="n">
-        <v>126.4499969482422</v>
+        <v>126.4199981689453</v>
       </c>
       <c r="C1142" t="n">
-        <v>225.7599945068359</v>
+        <v>223.6100006103516</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" s="2" t="n">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="B1143" t="n">
-        <v>125.4800033569336</v>
+        <v>126.4300003051758</v>
       </c>
       <c r="C1143" t="n">
-        <v>220.9700012207031</v>
+        <v>221.6199951171875</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" s="2" t="n">
-        <v>46248</v>
+        <v>46253</v>
       </c>
       <c r="B1144" t="n">
-        <v>125.129997253418</v>
+        <v>125.7300033569336</v>
       </c>
       <c r="C1144" t="n">
-        <v>221.2200012207031</v>
+        <v>216.4299926757812</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" s="2" t="n">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="B1145" t="n">
-        <v>126.4199981689453</v>
+        <v>128.8800048828125</v>
       </c>
       <c r="C1145" t="n">
-        <v>223.6100006103516</v>
+        <v>225.4299926757812</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" s="2" t="n">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="B1146" t="n">
-        <v>126.4300003051758</v>
+        <v>131.3200073242188</v>
       </c>
       <c r="C1146" t="n">
-        <v>221.6199951171875</v>
+        <v>232.9199981689453</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" s="2" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="B1147" t="n">
-        <v>125.7300033569336</v>
+        <v>133.0200042724609</v>
       </c>
       <c r="C1147" t="n">
-        <v>216.4299926757812</v>
+        <v>231.8000030517578</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" s="2" t="n">
-        <v>46254</v>
+        <v>46259</v>
       </c>
       <c r="B1148" t="n">
-        <v>128.8800048828125</v>
+        <v>132.7799987792969</v>
       </c>
       <c r="C1148" t="n">
-        <v>225.4299926757812</v>
+        <v>229</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" s="2" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="B1149" t="n">
-        <v>131.3200073242188</v>
+        <v>132.3699951171875</v>
       </c>
       <c r="C1149" t="n">
-        <v>232.9199981689453</v>
+        <v>230.1300048828125</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" s="2" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B1150" t="n">
-        <v>133.0200042724609</v>
+        <v>130.0500030517578</v>
       </c>
       <c r="C1150" t="n">
-        <v>231.8000030517578</v>
+        <v>226.3699951171875</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" s="2" t="n">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="B1151" t="n">
-        <v>132.7799987792969</v>
+        <v>130.8500061035156</v>
       </c>
       <c r="C1151" t="n">
-        <v>229</v>
+        <v>230.4199981689453</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" s="2" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="B1152" t="n">
-        <v>132.3699951171875</v>
+        <v>127.3199996948242</v>
       </c>
       <c r="C1152" t="n">
-        <v>230.1300048828125</v>
+        <v>223.2100067138672</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" s="2" t="n">
-        <v>46261</v>
+        <v>46266</v>
       </c>
       <c r="B1153" t="n">
-        <v>130.0500030517578</v>
+        <v>125.3399963378906</v>
       </c>
       <c r="C1153" t="n">
-        <v>226.3699951171875</v>
+        <v>217.7200012207031</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" s="2" t="n">
-        <v>46262</v>
+        <v>46267</v>
       </c>
       <c r="B1154" t="n">
-        <v>130.8500061035156</v>
+        <v>123.5199966430664</v>
       </c>
       <c r="C1154" t="n">
-        <v>230.4199981689453</v>
+        <v>215.4499969482422</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" s="2" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B1155" t="n">
-        <v>127.3199996948242</v>
+        <v>126.2300033569336</v>
       </c>
       <c r="C1155" t="n">
-        <v>223.2100067138672</v>
+        <v>219.8800048828125</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" s="2" t="n">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="B1156" t="n">
-        <v>125.3399963378906</v>
+        <v>127.1699981689453</v>
       </c>
       <c r="C1156" t="n">
-        <v>217.7200012207031</v>
+        <v>222.7799987792969</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" s="2" t="n">
-        <v>46267</v>
+        <v>46272</v>
       </c>
       <c r="B1157" t="n">
-        <v>123.5199966430664</v>
+        <v>125.5800018310547</v>
       </c>
       <c r="C1157" t="n">
-        <v>215.4499969482422</v>
+        <v>219.9600067138672</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B1158" t="n">
-        <v>126.2300033569336</v>
+        <v>125.8399963378906</v>
       </c>
       <c r="C1158" t="n">
-        <v>219.8800048828125</v>
+        <v>221.1699981689453</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" s="2" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B1159" t="n">
-        <v>127.1699981689453</v>
+        <v>125.7799987792969</v>
       </c>
       <c r="C1159" t="n">
-        <v>222.7799987792969</v>
+        <v>222.5899963378906</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" s="2" t="n">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B1160" t="n">
-        <v>125.5800018310547</v>
+        <v>126.1999969482422</v>
       </c>
       <c r="C1160" t="n">
-        <v>219.9600067138672</v>
+        <v>223.5299987792969</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" s="2" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B1161" t="n">
-        <v>125.8399963378906</v>
+        <v>125.120002746582</v>
       </c>
       <c r="C1161" t="n">
-        <v>221.1699981689453</v>
+        <v>216.7200012207031</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" s="2" t="n">
-        <v>46274</v>
+        <v>46280</v>
       </c>
       <c r="B1162" t="n">
-        <v>125.7799987792969</v>
+        <v>123.620002746582</v>
       </c>
       <c r="C1162" t="n">
-        <v>222.5899963378906</v>
+        <v>214.6699981689453</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" s="2" t="n">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="B1163" t="n">
-        <v>126.1999969482422</v>
+        <v>124.9100036621094</v>
       </c>
       <c r="C1163" t="n">
-        <v>223.5299987792969</v>
+        <v>218.4600067138672</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" s="2" t="n">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="B1164" t="n">
-        <v>125.120002746582</v>
+        <v>124.4300003051758</v>
       </c>
       <c r="C1164" t="n">
-        <v>216.7200012207031</v>
+        <v>216.6399993896484</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" s="2" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B1165" t="n">
-        <v>125.120002746582</v>
+        <v>126.4800033569336</v>
       </c>
       <c r="C1165" t="n">
-        <v>216.7200012207031</v>
+        <v>224.0700073242188</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" s="2" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B1166" t="n">
-        <v>123.620002746582</v>
+        <v>125.5699996948242</v>
       </c>
       <c r="C1166" t="n">
-        <v>214.6699981689453</v>
+        <v>222.2100067138672</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" s="2" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B1167" t="n">
-        <v>124.9100036621094</v>
+        <v>125</v>
       </c>
       <c r="C1167" t="n">
-        <v>218.4600067138672</v>
+        <v>220.2700042724609</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" s="2" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B1168" t="n">
-        <v>124.4300003051758</v>
+        <v>124.7300033569336</v>
       </c>
       <c r="C1168" t="n">
-        <v>216.6399993896484</v>
+        <v>220.2599945068359</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" s="2" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B1169" t="n">
-        <v>126.4800033569336</v>
+        <v>123.4300003051758</v>
       </c>
       <c r="C1169" t="n">
-        <v>224.0700073242188</v>
+        <v>215.9499969482422</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" s="2" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B1170" t="n">
-        <v>125.5699996948242</v>
+        <v>124.4300003051758</v>
       </c>
       <c r="C1170" t="n">
-        <v>222.2100067138672</v>
+        <v>218.8000030517578</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" s="2" t="n">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="B1171" t="n">
-        <v>125</v>
+        <v>121.1699981689453</v>
       </c>
       <c r="C1171" t="n">
-        <v>220.2700042724609</v>
+        <v>210.6499938964844</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" s="2" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="B1172" t="n">
-        <v>124.7300033569336</v>
+        <v>120.6399993896484</v>
       </c>
       <c r="C1172" t="n">
-        <v>220.2599945068359</v>
+        <v>209.1499938964844</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" s="2" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="B1173" t="n">
-        <v>123.4300003051758</v>
+        <v>121.5899963378906</v>
       </c>
       <c r="C1173" t="n">
-        <v>215.9499969482422</v>
+        <v>209.6199951171875</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" s="2" t="n">
-        <v>46290</v>
+        <v>46296</v>
       </c>
       <c r="B1174" t="n">
-        <v>124.4300003051758</v>
+        <v>121.4300003051758</v>
       </c>
       <c r="C1174" t="n">
-        <v>218.8000030517578</v>
+        <v>208.7100067138672</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" s="2" t="n">
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="B1175" t="n">
-        <v>121.1699981689453</v>
+        <v>121.5800018310547</v>
       </c>
       <c r="C1175" t="n">
-        <v>210.6499938964844</v>
+        <v>211.8500061035156</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" s="2" t="n">
-        <v>46294</v>
+        <v>46301</v>
       </c>
       <c r="B1176" t="n">
-        <v>120.6399993896484</v>
+        <v>121.4599990844727</v>
       </c>
       <c r="C1176" t="n">
-        <v>209.1499938964844</v>
+        <v>210.6999969482422</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" s="2" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="B1177" t="n">
-        <v>121.5899963378906</v>
+        <v>121.0800018310547</v>
       </c>
       <c r="C1177" t="n">
-        <v>209.6199951171875</v>
+        <v>209.0200042724609</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" s="2" t="n">
-        <v>46296</v>
+        <v>46304</v>
       </c>
       <c r="B1178" t="n">
-        <v>121.4300003051758</v>
+        <v>122.75</v>
       </c>
       <c r="C1178" t="n">
-        <v>208.7100067138672</v>
-      </c>
-    </row>
-    <row r="1179">
-      <c r="A1179" s="2" t="n">
-        <v>46297</v>
-      </c>
-      <c r="B1179" t="n">
-        <v>121.4300003051758</v>
-      </c>
-      <c r="C1179" t="n">
-        <v>208.7100067138672</v>
-      </c>
-    </row>
-    <row r="1180">
-      <c r="A1180" s="2" t="n">
-        <v>46300</v>
-      </c>
-      <c r="B1180" t="n">
-        <v>121.5800018310547</v>
-      </c>
-      <c r="C1180" t="n">
-        <v>211.8500061035156</v>
-      </c>
-    </row>
-    <row r="1181">
-      <c r="A1181" s="2" t="n">
-        <v>46301</v>
-      </c>
-      <c r="B1181" t="n">
-        <v>121.4599990844727</v>
-      </c>
-      <c r="C1181" t="n">
-        <v>210.6999969482422</v>
-      </c>
-    </row>
-    <row r="1182">
-      <c r="A1182" s="2" t="n">
-        <v>46303</v>
-      </c>
-      <c r="B1182" t="n">
-        <v>121.4599990844727</v>
-      </c>
-      <c r="C1182" t="n">
-        <v>210.6999969482422</v>
+        <v>209.6799926757812</v>
       </c>
     </row>
   </sheetData>
@@ -13399,10 +13355,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1069144315595794</v>
+        <v>0.9540288650768503</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5152188990610984</v>
+        <v>0.02862205895970416</v>
       </c>
     </row>
     <row r="3">
@@ -14071,10 +14027,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1069144315595794</v>
+        <v>0.9540288650768503</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5152188990610984</v>
+        <v>0.02862205895970416</v>
       </c>
     </row>
     <row r="3">
@@ -14303,7 +14259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C907"/>
+  <dimension ref="A1:C903"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23037,1256 +22993,1212 @@
     </row>
     <row r="794">
       <c r="A794" s="2" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B794" t="n">
-        <v>53.3101441188893</v>
+        <v>52.00595454753503</v>
       </c>
       <c r="C794" t="n">
-        <v>140.3592142973158</v>
+        <v>143.3808736361903</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" s="2" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B795" t="n">
-        <v>52.91765477956836</v>
+        <v>52.64276586957939</v>
       </c>
       <c r="C795" t="n">
-        <v>143.3808736361903</v>
+        <v>141.8277820387209</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" s="2" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B796" t="n">
-        <v>54.53510303108449</v>
+        <v>56.88803523747443</v>
       </c>
       <c r="C796" t="n">
-        <v>145.6955671876428</v>
+        <v>151.7067370925162</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" s="2" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B797" t="n">
-        <v>54.94752027046412</v>
+        <v>55.50974487377422</v>
       </c>
       <c r="C797" t="n">
-        <v>147.6919932698214</v>
+        <v>152.9206792780419</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" s="2" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B798" t="n">
-        <v>57.37767983821709</v>
+        <v>57.17537402266765</v>
       </c>
       <c r="C798" t="n">
-        <v>161.3403135379613</v>
+        <v>162.1370781151882</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" s="2" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B799" t="n">
-        <v>58.5991348745204</v>
+        <v>57.22123969781055</v>
       </c>
       <c r="C799" t="n">
-        <v>162.423521610936</v>
+        <v>163.647292544359</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" s="2" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B800" t="n">
-        <v>54.85046559630169</v>
+        <v>56.58456615129748</v>
       </c>
       <c r="C800" t="n">
-        <v>163.9645373804428</v>
+        <v>175.6919203705243</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" s="2" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B801" t="n">
-        <v>51.72288418062223</v>
+        <v>60.40424923754821</v>
       </c>
       <c r="C801" t="n">
-        <v>170.9202360798198</v>
+        <v>189.6366621701191</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" s="2" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B802" t="n">
-        <v>62.08170210593069</v>
+        <v>62.13090644492362</v>
       </c>
       <c r="C802" t="n">
-        <v>190.3858773145978</v>
+        <v>192.0133608971734</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" s="2" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B803" t="n">
-        <v>62.81195305707399</v>
+        <v>59.88386429292652</v>
       </c>
       <c r="C803" t="n">
-        <v>192.6125968156114</v>
+        <v>169.8455729404425</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" s="2" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B804" t="n">
-        <v>60.16088957226102</v>
+        <v>60.51979214055307</v>
       </c>
       <c r="C804" t="n">
-        <v>168.5692888121567</v>
+        <v>172.1272782800984</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" s="2" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B805" t="n">
-        <v>66.32468756711063</v>
+        <v>67.53012793764208</v>
       </c>
       <c r="C805" t="n">
-        <v>176.859139220093</v>
+        <v>176.9575604093841</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" s="2" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B806" t="n">
-        <v>65.22069039314779</v>
+        <v>64.66421835178639</v>
       </c>
       <c r="C806" t="n">
-        <v>169.6730807414299</v>
+        <v>169.0448235644699</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" s="2" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B807" t="n">
-        <v>65.69100778105017</v>
+        <v>66.37821639945017</v>
       </c>
       <c r="C807" t="n">
-        <v>170.7168099272865</v>
+        <v>169.9774952076155</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" s="2" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B808" t="n">
-        <v>69.70405495778431</v>
+        <v>69.39252135146047</v>
       </c>
       <c r="C808" t="n">
-        <v>175.3770505144296</v>
+        <v>175.9999926624402</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" s="2" t="n">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B809" t="n">
-        <v>67.78092317833244</v>
+        <v>67.79377289161708</v>
       </c>
       <c r="C809" t="n">
-        <v>173.6967621913421</v>
+        <v>177.4791460865802</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" s="2" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B810" t="n">
-        <v>66.63686799715435</v>
+        <v>65.44944118483953</v>
       </c>
       <c r="C810" t="n">
-        <v>175.86467569688</v>
+        <v>170.7574613688421</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" s="2" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B811" t="n">
-        <v>65.72451436890401</v>
+        <v>65.0338780623934</v>
       </c>
       <c r="C811" t="n">
-        <v>171.6354853349614</v>
+        <v>170.1005181571916</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" s="2" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B812" t="n">
-        <v>62.31445696368907</v>
+        <v>61.82389169369105</v>
       </c>
       <c r="C812" t="n">
-        <v>165.0859213392121</v>
+        <v>164.5554736533767</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" s="2" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B813" t="n">
-        <v>61.68399603244706</v>
+        <v>59.74188919147725</v>
       </c>
       <c r="C813" t="n">
-        <v>164.5526767503382</v>
+        <v>164.2032835881177</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" s="2" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B814" t="n">
-        <v>61.8035347000226</v>
+        <v>61.82869414150603</v>
       </c>
       <c r="C814" t="n">
-        <v>165.2308062335775</v>
+        <v>167.5601005535085</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" s="2" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B815" t="n">
-        <v>59.82199226386822</v>
+        <v>60.01003480140283</v>
       </c>
       <c r="C815" t="n">
-        <v>163.9238341954697</v>
+        <v>161.0153202755975</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" s="2" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B816" t="n">
-        <v>61.72700115303975</v>
+        <v>61.51332823428417</v>
       </c>
       <c r="C816" t="n">
-        <v>167.4747361998008</v>
+        <v>162.1584152665112</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" s="2" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B817" t="n">
-        <v>59.43043127903191</v>
+        <v>59.60529937036052</v>
       </c>
       <c r="C817" t="n">
-        <v>160.0800873364271</v>
+        <v>156.6972319504798</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" s="2" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B818" t="n">
-        <v>62.452594789924</v>
+        <v>56.96587365008663</v>
       </c>
       <c r="C818" t="n">
-        <v>160.5516270895677</v>
+        <v>140.8644185684456</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" s="2" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B819" t="n">
-        <v>60.74978263087522</v>
+        <v>57.74311581256126</v>
       </c>
       <c r="C819" t="n">
-        <v>158.1664078117238</v>
+        <v>145.7869609400061</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" s="2" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B820" t="n">
-        <v>54.19772583013491</v>
+        <v>50.45952133222195</v>
       </c>
       <c r="C820" t="n">
-        <v>140.8898605575392</v>
+        <v>133.1325194828945</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" s="2" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B821" t="n">
-        <v>54.85982153793967</v>
+        <v>47.31381620480735</v>
       </c>
       <c r="C821" t="n">
-        <v>138.6784532274788</v>
+        <v>127.8509639138133</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" s="2" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B822" t="n">
-        <v>48.99766961445988</v>
+        <v>49.94465850412444</v>
       </c>
       <c r="C822" t="n">
-        <v>124.8623850856456</v>
+        <v>134.2099878497419</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" s="2" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B823" t="n">
-        <v>45.94395433752019</v>
+        <v>51.85365901471317</v>
       </c>
       <c r="C823" t="n">
-        <v>119.7974604842514</v>
+        <v>136.9142099137891</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" s="2" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B824" t="n">
-        <v>50.09232196287792</v>
+        <v>52.82530377865871</v>
       </c>
       <c r="C824" t="n">
-        <v>124.353077131902</v>
+        <v>130.5731827350555</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" s="2" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B825" t="n">
-        <v>54.21222096614029</v>
+        <v>53.76490412302968</v>
       </c>
       <c r="C825" t="n">
-        <v>131.6923973848637</v>
+        <v>127.8570764506239</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" s="2" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B826" t="n">
-        <v>54.00074240131807</v>
+        <v>51.49485401554499</v>
       </c>
       <c r="C826" t="n">
-        <v>127.3322409155156</v>
+        <v>121.4210064615909</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" s="2" t="n">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="B827" t="n">
-        <v>53.23179386653756</v>
+        <v>48.32837759644792</v>
       </c>
       <c r="C827" t="n">
-        <v>128.3226317922619</v>
+        <v>115.4310184848399</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" s="2" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B828" t="n">
-        <v>50.04300732568112</v>
+        <v>48.81435514789627</v>
       </c>
       <c r="C828" t="n">
-        <v>125.3478453799926</v>
+        <v>120.5957326820365</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" s="2" t="n">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="B829" t="n">
-        <v>44.09960889371023</v>
+        <v>43.02899729855365</v>
       </c>
       <c r="C829" t="n">
-        <v>113.4991805260714</v>
+        <v>107.3666950699957</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" s="2" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B830" t="n">
-        <v>45.76965710052509</v>
+        <v>41.48513989641873</v>
       </c>
       <c r="C830" t="n">
-        <v>117.3795501139695</v>
+        <v>105.9959512717634</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" s="2" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B831" t="n">
-        <v>44.01647897517711</v>
+        <v>39.24418905521922</v>
       </c>
       <c r="C831" t="n">
-        <v>106.4113566745887</v>
+        <v>98.26279151916553</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" s="2" t="n">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="B832" t="n">
-        <v>41.99782130518766</v>
+        <v>40.63292549540149</v>
       </c>
       <c r="C832" t="n">
-        <v>100.8378041622177</v>
+        <v>95.82038755426956</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" s="2" t="n">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="B833" t="n">
-        <v>38.85734728010106</v>
+        <v>40.0773039476472</v>
       </c>
       <c r="C833" t="n">
-        <v>98.37704098031972</v>
+        <v>104.37915388232</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" s="2" t="n">
-        <v>46199</v>
+        <v>46204</v>
       </c>
       <c r="B834" t="n">
-        <v>39.80298478825159</v>
+        <v>40.4110353532378</v>
       </c>
       <c r="C834" t="n">
-        <v>99.95161378942015</v>
+        <v>104.5687748835984</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" s="2" t="n">
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="B835" t="n">
-        <v>40.85409526608365</v>
+        <v>42.37841426004476</v>
       </c>
       <c r="C835" t="n">
-        <v>100.4818812545354</v>
+        <v>108.4425542853542</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" s="2" t="n">
-        <v>46203</v>
+        <v>46206</v>
       </c>
       <c r="B836" t="n">
-        <v>43.20819512632639</v>
+        <v>48.56753836907897</v>
       </c>
       <c r="C836" t="n">
-        <v>107.2047602192922</v>
+        <v>115.4707424119242</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" s="2" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B837" t="n">
-        <v>42.34989300411522</v>
+        <v>47.34311581422692</v>
       </c>
       <c r="C837" t="n">
-        <v>107.4401276358499</v>
+        <v>116.2936852679967</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" s="2" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B838" t="n">
-        <v>45.08135904416631</v>
+        <v>46.17849829406104</v>
       </c>
       <c r="C838" t="n">
-        <v>108.1016050651604</v>
+        <v>108.111221640554</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" s="2" t="n">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="B839" t="n">
-        <v>50.74552216376939</v>
+        <v>46.54805495840875</v>
       </c>
       <c r="C839" t="n">
-        <v>117.6962321329133</v>
+        <v>106.7184598920207</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" s="2" t="n">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="B840" t="n">
-        <v>49.40618243266766</v>
+        <v>48.04350710275762</v>
       </c>
       <c r="C840" t="n">
-        <v>115.0483048553237</v>
+        <v>107.8169165720841</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" s="2" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="B841" t="n">
-        <v>46.30474690461214</v>
+        <v>45.76186914416929</v>
       </c>
       <c r="C841" t="n">
-        <v>109.1374947936131</v>
+        <v>101.9241979582258</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" s="2" t="n">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="B842" t="n">
-        <v>44.19923339212228</v>
+        <v>44.18690182245737</v>
       </c>
       <c r="C842" t="n">
-        <v>104.625121851166</v>
+        <v>102.005854799023</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" s="2" t="n">
-        <v>46212</v>
+        <v>46217</v>
       </c>
       <c r="B843" t="n">
-        <v>46.17947789928994</v>
+        <v>43.16751055245724</v>
       </c>
       <c r="C843" t="n">
-        <v>105.0158768819803</v>
+        <v>100.2599297261314</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" s="2" t="n">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="B844" t="n">
-        <v>46.05019196571649</v>
+        <v>43.88676012840094</v>
       </c>
       <c r="C844" t="n">
-        <v>100.9913366353901</v>
+        <v>100.8277195358244</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" s="2" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="B845" t="n">
-        <v>45.22538025706313</v>
+        <v>44.62933439239778</v>
       </c>
       <c r="C845" t="n">
-        <v>99.88438663057228</v>
+        <v>99.28701658479959</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" s="2" t="n">
-        <v>46217</v>
+        <v>46220</v>
       </c>
       <c r="B846" t="n">
-        <v>43.57514868724921</v>
+        <v>43.3399389270642</v>
       </c>
       <c r="C846" t="n">
-        <v>99.83668154969141</v>
+        <v>96.8681000849942</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" s="2" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="B847" t="n">
-        <v>45.43296409465598</v>
+        <v>45.99524943153717</v>
       </c>
       <c r="C847" t="n">
-        <v>101.4287199909734</v>
+        <v>100.6854008485059</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" s="2" t="n">
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="B848" t="n">
-        <v>44.30678050039791</v>
+        <v>45.86792800445343</v>
       </c>
       <c r="C848" t="n">
-        <v>99.44074646979577</v>
+        <v>104.6379303838157</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" s="2" t="n">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="B849" t="n">
-        <v>42.68638168614412</v>
+        <v>46.81453746079654</v>
       </c>
       <c r="C849" t="n">
-        <v>92.07047847007652</v>
+        <v>99.70944085528164</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" s="2" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B850" t="n">
-        <v>42.69662952756548</v>
+        <v>44.95604106343776</v>
       </c>
       <c r="C850" t="n">
-        <v>88.95655856461973</v>
+        <v>91.78331797676663</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" s="2" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="B851" t="n">
-        <v>44.15330720761539</v>
+        <v>44.37370675360708</v>
       </c>
       <c r="C851" t="n">
-        <v>96.09164662743481</v>
+        <v>94.91822985363729</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" s="2" t="n">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="B852" t="n">
-        <v>46.45359757142347</v>
+        <v>45.81438840999756</v>
       </c>
       <c r="C852" t="n">
-        <v>97.67140320482699</v>
+        <v>97.61572752352714</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" s="2" t="n">
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="B853" t="n">
-        <v>46.24198753802946</v>
+        <v>43.9502175448993</v>
       </c>
       <c r="C853" t="n">
-        <v>96.93858615084724</v>
+        <v>92.45846380708926</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" s="2" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="B854" t="n">
-        <v>44.26770931009199</v>
+        <v>42.97074963255594</v>
       </c>
       <c r="C854" t="n">
-        <v>93.34616949296657</v>
+        <v>89.4326837917706</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" s="2" t="n">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="B855" t="n">
-        <v>44.42957106228989</v>
+        <v>42.9075936584151</v>
       </c>
       <c r="C855" t="n">
-        <v>94.7608934420483</v>
+        <v>88.92749354828922</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" s="2" t="n">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="B856" t="n">
-        <v>41.15018312114606</v>
+        <v>41.48846847894827</v>
       </c>
       <c r="C856" t="n">
-        <v>87.11433998050697</v>
+        <v>87.39564448792845</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" s="2" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="B857" t="n">
-        <v>39.52238623775652</v>
+        <v>40.01194284923042</v>
       </c>
       <c r="C857" t="n">
-        <v>84.52816578828617</v>
+        <v>84.31389430485905</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" s="2" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="B858" t="n">
-        <v>42.61239173073781</v>
+        <v>42.34507555510565</v>
       </c>
       <c r="C858" t="n">
-        <v>86.30420887219242</v>
+        <v>86.95338495814462</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" s="2" t="n">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="B859" t="n">
-        <v>42.64312154313381</v>
+        <v>45.42022120412292</v>
       </c>
       <c r="C859" t="n">
-        <v>86.58293633667328</v>
+        <v>92.79905927111709</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" s="2" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B860" t="n">
-        <v>42.94770679165865</v>
+        <v>49.31123391391014</v>
       </c>
       <c r="C860" t="n">
-        <v>89.31681904699803</v>
+        <v>96.72626572736146</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" s="2" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="B861" t="n">
-        <v>43.02282540376829</v>
+        <v>50.65315103014984</v>
       </c>
       <c r="C861" t="n">
-        <v>89.32616185086665</v>
+        <v>101.3057048743626</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" s="2" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B862" t="n">
-        <v>44.90836299805667</v>
+        <v>51.20767417642078</v>
       </c>
       <c r="C862" t="n">
-        <v>94.20277095339173</v>
+        <v>100.6370697347369</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" s="2" t="n">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="B863" t="n">
-        <v>49.00244270575096</v>
+        <v>52.70073151231498</v>
       </c>
       <c r="C863" t="n">
-        <v>100.682877190944</v>
+        <v>107.9700693646841</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" s="2" t="n">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="B864" t="n">
-        <v>50.57962918999939</v>
+        <v>54.30140531683634</v>
       </c>
       <c r="C864" t="n">
-        <v>108.5611608458401</v>
+        <v>113.5654114673027</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" s="2" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="B865" t="n">
-        <v>49.68160135328936</v>
+        <v>50.76294400567305</v>
       </c>
       <c r="C865" t="n">
-        <v>103.9596763651528</v>
+        <v>104.431500330473</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" s="2" t="n">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="B866" t="n">
-        <v>50.12557795332209</v>
+        <v>49.65912730531174</v>
       </c>
       <c r="C866" t="n">
-        <v>104.6015091399666</v>
+        <v>103.5891715120974</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" s="2" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B867" t="n">
-        <v>51.54601300142421</v>
+        <v>51.5100604865403</v>
       </c>
       <c r="C867" t="n">
-        <v>106.777792522257</v>
+        <v>104.808572985277</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" s="2" t="n">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="B868" t="n">
-        <v>49.48772898180942</v>
+        <v>50.61948609476082</v>
       </c>
       <c r="C868" t="n">
-        <v>99.82817648918424</v>
+        <v>100.4159806904153</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" s="2" t="n">
-        <v>46248</v>
+        <v>46253</v>
       </c>
       <c r="B869" t="n">
-        <v>48.32858742068766</v>
+        <v>49.0398322039671</v>
       </c>
       <c r="C869" t="n">
-        <v>99.35117490061917</v>
+        <v>95.03468531583918</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" s="2" t="n">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="B870" t="n">
-        <v>51.89233818337185</v>
+        <v>54.84801115543385</v>
       </c>
       <c r="C870" t="n">
-        <v>104.1727606503794</v>
+        <v>105.834550388523</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" s="2" t="n">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="B871" t="n">
-        <v>52.362009147366</v>
+        <v>58.25500362943284</v>
       </c>
       <c r="C871" t="n">
-        <v>102.8372604650523</v>
+        <v>113.1795658200059</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" s="2" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="B872" t="n">
-        <v>51.13595344042672</v>
+        <v>59.89902676845307</v>
       </c>
       <c r="C872" t="n">
-        <v>94.54381364115167</v>
+        <v>108.3595533049508</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" s="2" t="n">
-        <v>46254</v>
+        <v>46259</v>
       </c>
       <c r="B873" t="n">
-        <v>55.01564328716972</v>
+        <v>59.70651882856399</v>
       </c>
       <c r="C873" t="n">
-        <v>103.4015960943669</v>
+        <v>106.6227521579215</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" s="2" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="B874" t="n">
-        <v>58.694872899358</v>
+        <v>59.96374032288521</v>
       </c>
       <c r="C874" t="n">
-        <v>111.6300230198927</v>
+        <v>109.0950481443504</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" s="2" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B875" t="n">
-        <v>61.6085630154082</v>
+        <v>58.00025137794413</v>
       </c>
       <c r="C875" t="n">
-        <v>111.8636279070286</v>
+        <v>106.9006375470797</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" s="2" t="n">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="B876" t="n">
-        <v>61.76900075197125</v>
+        <v>59.41764520527699</v>
       </c>
       <c r="C876" t="n">
-        <v>114.0386994787924</v>
+        <v>115.3659246374968</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" s="2" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="B877" t="n">
-        <v>60.35129039812777</v>
+        <v>54.23379162687152</v>
       </c>
       <c r="C877" t="n">
-        <v>110.8962601634656</v>
+        <v>104.5546197723669</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" s="2" t="n">
-        <v>46261</v>
+        <v>46266</v>
       </c>
       <c r="B878" t="n">
-        <v>57.40740586835427</v>
+        <v>51.70659909361466</v>
       </c>
       <c r="C878" t="n">
-        <v>105.9219453186242</v>
+        <v>98.05330721030873</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" s="2" t="n">
-        <v>46262</v>
+        <v>46267</v>
       </c>
       <c r="B879" t="n">
-        <v>56.70659413594685</v>
+        <v>47.9281396922951</v>
       </c>
       <c r="C879" t="n">
-        <v>105.6403318994203</v>
+        <v>92.28022407881787</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" s="2" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B880" t="n">
-        <v>51.878798656615</v>
+        <v>50.57855254653221</v>
       </c>
       <c r="C880" t="n">
-        <v>99.45491860388698</v>
+        <v>96.47931166788062</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" s="2" t="n">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="B881" t="n">
-        <v>48.47192496623165</v>
+        <v>50.63965994697923</v>
       </c>
       <c r="C881" t="n">
-        <v>93.04841601104023</v>
+        <v>97.53502499611022</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" s="2" t="n">
-        <v>46267</v>
+        <v>46272</v>
       </c>
       <c r="B882" t="n">
-        <v>44.7386945670913</v>
+        <v>47.15257466597483</v>
       </c>
       <c r="C882" t="n">
-        <v>89.69008053787029</v>
+        <v>93.66085857354372</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B883" t="n">
-        <v>45.74529784941104</v>
+        <v>45.29499532511299</v>
       </c>
       <c r="C883" t="n">
-        <v>85.41193327666777</v>
+        <v>86.49970908067178</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" s="2" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B884" t="n">
-        <v>46.83061687191126</v>
+        <v>45.22572207933195</v>
       </c>
       <c r="C884" t="n">
-        <v>88.94071059289408</v>
+        <v>88.77956867490148</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" s="2" t="n">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B885" t="n">
-        <v>42.8994148337555</v>
+        <v>43.6049168098191</v>
       </c>
       <c r="C885" t="n">
-        <v>84.90249529816754</v>
+        <v>87.9034973937498</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" s="2" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B886" t="n">
-        <v>42.74046178604674</v>
+        <v>41.92377217465775</v>
       </c>
       <c r="C886" t="n">
-        <v>85.81030029163863</v>
+        <v>82.07174951126494</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" s="2" t="n">
-        <v>46274</v>
+        <v>46280</v>
       </c>
       <c r="B887" t="n">
-        <v>41.88380892760492</v>
+        <v>39.44726522141639</v>
       </c>
       <c r="C887" t="n">
-        <v>87.03469653171871</v>
+        <v>80.37979524041438</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" s="2" t="n">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="B888" t="n">
-        <v>40.25338101803659</v>
+        <v>38.81973661038343</v>
       </c>
       <c r="C888" t="n">
-        <v>85.88773287259615</v>
+        <v>81.6715232547752</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" s="2" t="n">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="B889" t="n">
-        <v>37.23813234560414</v>
+        <v>36.48130174862681</v>
       </c>
       <c r="C889" t="n">
-        <v>80.31449939137505</v>
+        <v>80.24793659128385</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" s="2" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B890" t="n">
-        <v>37.64576528743051</v>
+        <v>39.14191554873096</v>
       </c>
       <c r="C890" t="n">
-        <v>81.59879995898258</v>
+        <v>87.75767906830092</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" s="2" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B891" t="n">
-        <v>36.41580114744003</v>
+        <v>38.56764057487343</v>
       </c>
       <c r="C891" t="n">
-        <v>79.94131825446109</v>
+        <v>86.2615264288487</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" s="2" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B892" t="n">
-        <v>36.8726722969468</v>
+        <v>36.97128761119617</v>
       </c>
       <c r="C892" t="n">
-        <v>76.66181485065364</v>
+        <v>78.12550359801891</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" s="2" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B893" t="n">
-        <v>36.85658030256776</v>
+        <v>37.1865440704952</v>
       </c>
       <c r="C893" t="n">
-        <v>76.01559649553673</v>
+        <v>78.95676895518331</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" s="2" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B894" t="n">
-        <v>37.07598131406012</v>
+        <v>33.77046146717389</v>
       </c>
       <c r="C894" t="n">
-        <v>79.80260181816146</v>
+        <v>73.28678557918349</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" s="2" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B895" t="n">
-        <v>37.61095856967038</v>
+        <v>36.36164417005565</v>
       </c>
       <c r="C895" t="n">
-        <v>82.49835973659792</v>
+        <v>79.69776545088649</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" s="2" t="n">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="B896" t="n">
-        <v>36.4628843692777</v>
+        <v>32.28165959323499</v>
       </c>
       <c r="C896" t="n">
-        <v>79.02308406490219</v>
+        <v>71.20448011139511</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" s="2" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="B897" t="n">
-        <v>36.63052043602126</v>
+        <v>32.15028828981972</v>
       </c>
       <c r="C897" t="n">
-        <v>78.13181705520429</v>
+        <v>69.14677825758946</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" s="2" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="B898" t="n">
-        <v>32.52093742110736</v>
+        <v>30.54541242718123</v>
       </c>
       <c r="C898" t="n">
-        <v>68.42145912674791</v>
+        <v>63.48463041766144</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" s="2" t="n">
-        <v>46290</v>
+        <v>46296</v>
       </c>
       <c r="B899" t="n">
-        <v>30.79996204951543</v>
+        <v>27.64638264594597</v>
       </c>
       <c r="C899" t="n">
-        <v>68.64497748405466</v>
+        <v>60.86788798915536</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" s="2" t="n">
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="B900" t="n">
-        <v>28.03254326964701</v>
+        <v>28.46576776748469</v>
       </c>
       <c r="C900" t="n">
-        <v>62.05091545100525</v>
+        <v>62.97407273719704</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" s="2" t="n">
-        <v>46294</v>
+        <v>46301</v>
       </c>
       <c r="B901" t="n">
-        <v>27.7560086834354</v>
+        <v>28.62437646080929</v>
       </c>
       <c r="C901" t="n">
-        <v>58.00408069164264</v>
+        <v>59.17504322766571</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" s="2" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="B902" t="n">
-        <v>29.04902861662608</v>
+        <v>28.50774810269221</v>
       </c>
       <c r="C902" t="n">
-        <v>57.59717598245165</v>
+        <v>57.14608894425488</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" s="2" t="n">
-        <v>46296</v>
+        <v>46304</v>
       </c>
       <c r="B903" t="n">
-        <v>26.62147901260203</v>
+        <v>27.99791245767138</v>
       </c>
       <c r="C903" t="n">
-        <v>50.08630114920432</v>
-      </c>
-    </row>
-    <row r="904">
-      <c r="A904" s="2" t="n">
-        <v>46297</v>
-      </c>
-      <c r="B904" t="n">
-        <v>26.68753493820986</v>
-      </c>
-      <c r="C904" t="n">
-        <v>53.38428417701675</v>
-      </c>
-    </row>
-    <row r="905">
-      <c r="A905" s="2" t="n">
-        <v>46300</v>
-      </c>
-      <c r="B905" t="n">
-        <v>24.53139941760907</v>
-      </c>
-      <c r="C905" t="n">
-        <v>51.46208157512338</v>
-      </c>
-    </row>
-    <row r="906">
-      <c r="A906" s="2" t="n">
-        <v>46301</v>
-      </c>
-      <c r="B906" t="n">
-        <v>25.12619703958743</v>
-      </c>
-      <c r="C906" t="n">
-        <v>50.75844678710004</v>
-      </c>
-    </row>
-    <row r="907">
-      <c r="A907" s="2" t="n">
-        <v>46303</v>
-      </c>
-      <c r="B907" t="n">
-        <v>22.41483328981149</v>
-      </c>
-      <c r="C907" t="n">
-        <v>46.6555297790667</v>
+        <v>50.78383169640956</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -12961,7 +12961,7 @@
         <v>46255</v>
       </c>
       <c r="B1146" t="n">
-        <v>131.3200073242188</v>
+        <v>128.8800048828125</v>
       </c>
       <c r="C1146" t="n">
         <v>232.9199981689453</v>
@@ -23843,7 +23843,7 @@
         <v>46255</v>
       </c>
       <c r="B871" t="n">
-        <v>58.25500362943284</v>
+        <v>55.3145332236765</v>
       </c>
       <c r="C871" t="n">
         <v>113.1795658200059</v>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13313,10 +13313,10 @@
         <v>46304</v>
       </c>
       <c r="B1178" t="n">
-        <v>122.75</v>
+        <v>121.0800018310547</v>
       </c>
       <c r="C1178" t="n">
-        <v>209.6799926757812</v>
+        <v>209.0200042724609</v>
       </c>
     </row>
   </sheetData>
@@ -13355,10 +13355,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9540288650768503</v>
+        <v>-0.4194378832109602</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02862205895970416</v>
+        <v>-0.2862278688591458</v>
       </c>
     </row>
     <row r="3">
@@ -14027,10 +14027,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9540288650768503</v>
+        <v>-0.4194378832109602</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02862205895970416</v>
+        <v>-0.2862278688591458</v>
       </c>
     </row>
     <row r="3">
@@ -24195,10 +24195,10 @@
         <v>46304</v>
       </c>
       <c r="B903" t="n">
-        <v>27.99791245767138</v>
+        <v>26.25651710587395</v>
       </c>
       <c r="C903" t="n">
-        <v>50.78383169640956</v>
+        <v>50.30922475342998</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1178"/>
+  <dimension ref="A1:C1179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12961,7 +12961,7 @@
         <v>46255</v>
       </c>
       <c r="B1146" t="n">
-        <v>128.8800048828125</v>
+        <v>131.3200073242188</v>
       </c>
       <c r="C1146" t="n">
         <v>232.9199981689453</v>
@@ -13310,13 +13310,24 @@
     </row>
     <row r="1178">
       <c r="A1178" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1178" t="n">
+        <v>120.9400024414062</v>
+      </c>
+      <c r="C1178" t="n">
+        <v>205.8699951171875</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="2" t="n">
         <v>46304</v>
       </c>
-      <c r="B1178" t="n">
-        <v>121.0800018310547</v>
-      </c>
-      <c r="C1178" t="n">
-        <v>209.0200042724609</v>
+      <c r="B1179" t="n">
+        <v>120.9400024414062</v>
+      </c>
+      <c r="C1179" t="n">
+        <v>205.8699951171875</v>
       </c>
     </row>
   </sheetData>
@@ -13355,10 +13366,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.4194378832109602</v>
+        <v>-0.5345784324872316</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2862278688591458</v>
+        <v>-1.788951477602874</v>
       </c>
     </row>
     <row r="3">
@@ -14027,10 +14038,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.4194378832109602</v>
+        <v>-0.5345784324872316</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2862278688591458</v>
+        <v>-1.788951477602874</v>
       </c>
     </row>
     <row r="3">
@@ -14259,7 +14270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C903"/>
+  <dimension ref="A1:C904"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23843,7 +23854,7 @@
         <v>46255</v>
       </c>
       <c r="B871" t="n">
-        <v>55.3145332236765</v>
+        <v>58.25500362943284</v>
       </c>
       <c r="C871" t="n">
         <v>113.1795658200059</v>
@@ -24192,13 +24203,24 @@
     </row>
     <row r="903">
       <c r="A903" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B903" t="n">
+        <v>26.11053234318273</v>
+      </c>
+      <c r="C903" t="n">
+        <v>48.04400886778597</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="2" t="n">
         <v>46304</v>
       </c>
-      <c r="B903" t="n">
-        <v>26.25651710587395</v>
-      </c>
-      <c r="C903" t="n">
-        <v>50.30922475342998</v>
+      <c r="B904" t="n">
+        <v>26.17632171800117</v>
+      </c>
+      <c r="C904" t="n">
+        <v>51.29711474671554</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13324,10 +13324,10 @@
         <v>46304</v>
       </c>
       <c r="B1179" t="n">
-        <v>120.9400024414062</v>
+        <v>122.75</v>
       </c>
       <c r="C1179" t="n">
-        <v>205.8699951171875</v>
+        <v>209.6799926757812</v>
       </c>
     </row>
   </sheetData>
@@ -13366,10 +13366,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.5345784324872316</v>
+        <v>0.9540288650768503</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.788951477602874</v>
+        <v>0.02862205895970416</v>
       </c>
     </row>
     <row r="3">
@@ -14038,10 +14038,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.5345784324872316</v>
+        <v>0.9540288650768503</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.788951477602874</v>
+        <v>0.02862205895970416</v>
       </c>
     </row>
     <row r="3">
@@ -24217,10 +24217,10 @@
         <v>46304</v>
       </c>
       <c r="B904" t="n">
-        <v>26.17632171800117</v>
+        <v>28.06468644143145</v>
       </c>
       <c r="C904" t="n">
-        <v>51.29711474671554</v>
+        <v>54.09714219840485</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -12961,7 +12961,7 @@
         <v>46255</v>
       </c>
       <c r="B1146" t="n">
-        <v>131.3200073242188</v>
+        <v>128.8800048828125</v>
       </c>
       <c r="C1146" t="n">
         <v>232.9199981689453</v>
@@ -23854,7 +23854,7 @@
         <v>46255</v>
       </c>
       <c r="B871" t="n">
-        <v>58.25500362943284</v>
+        <v>55.3145332236765</v>
       </c>
       <c r="C871" t="n">
         <v>113.1795658200059</v>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1179"/>
+  <dimension ref="A1:C1180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12961,7 +12961,7 @@
         <v>46255</v>
       </c>
       <c r="B1146" t="n">
-        <v>128.8800048828125</v>
+        <v>131.3200073242188</v>
       </c>
       <c r="C1146" t="n">
         <v>232.9199981689453</v>
@@ -13328,6 +13328,17 @@
       </c>
       <c r="C1179" t="n">
         <v>209.6799926757812</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1180" t="n">
+        <v>121.2399978637695</v>
+      </c>
+      <c r="C1180" t="n">
+        <v>208.6399993896484</v>
       </c>
     </row>
   </sheetData>
@@ -13366,10 +13377,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9540288650768503</v>
+        <v>-0.2878513731906618</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02862205895970416</v>
+        <v>-0.4675106146201369</v>
       </c>
     </row>
     <row r="3">
@@ -14038,10 +14049,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9540288650768503</v>
+        <v>-0.2878513731906618</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02862205895970416</v>
+        <v>-0.4675106146201369</v>
       </c>
     </row>
     <row r="3">
@@ -14270,7 +14281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C904"/>
+  <dimension ref="A1:C905"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23854,7 +23865,7 @@
         <v>46255</v>
       </c>
       <c r="B871" t="n">
-        <v>55.3145332236765</v>
+        <v>58.25500362943284</v>
       </c>
       <c r="C871" t="n">
         <v>113.1795658200059</v>
@@ -24221,6 +24232,17 @@
       </c>
       <c r="C904" t="n">
         <v>54.09714219840485</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B905" t="n">
+        <v>24.18314173364886</v>
+      </c>
+      <c r="C905" t="n">
+        <v>49.16708849159767</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13335,10 +13335,10 @@
         <v>46307</v>
       </c>
       <c r="B1180" t="n">
-        <v>121.2399978637695</v>
+        <v>122.75</v>
       </c>
       <c r="C1180" t="n">
-        <v>208.6399993896484</v>
+        <v>209.6799926757812</v>
       </c>
     </row>
   </sheetData>
@@ -13377,10 +13377,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.2878513731906618</v>
+        <v>0.9540288650768503</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4675106146201369</v>
+        <v>0.02862205895970416</v>
       </c>
     </row>
     <row r="3">
@@ -14049,10 +14049,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.2878513731906618</v>
+        <v>0.9540288650768503</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4675106146201369</v>
+        <v>0.02862205895970416</v>
       </c>
     </row>
     <row r="3">
@@ -24239,10 +24239,10 @@
         <v>46307</v>
       </c>
       <c r="B905" t="n">
-        <v>24.18314173364886</v>
+        <v>25.72979970631166</v>
       </c>
       <c r="C905" t="n">
-        <v>49.16708849159767</v>
+        <v>49.91063129737348</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13332,13 +13332,13 @@
     </row>
     <row r="1180">
       <c r="A1180" s="2" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B1180" t="n">
-        <v>122.75</v>
+        <v>121</v>
       </c>
       <c r="C1180" t="n">
-        <v>209.6799926757812</v>
+        <v>207.6199951171875</v>
       </c>
     </row>
   </sheetData>
@@ -13377,10 +13377,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9540288650768503</v>
+        <v>-0.4852342755657824</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02862205895970416</v>
+        <v>-0.9541074547215311</v>
       </c>
     </row>
     <row r="3">
@@ -14049,10 +14049,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9540288650768503</v>
+        <v>-0.4852342755657824</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02862205895970416</v>
+        <v>-0.9541074547215311</v>
       </c>
     </row>
     <row r="3">
@@ -24236,13 +24236,13 @@
     </row>
     <row r="905">
       <c r="A905" s="2" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B905" t="n">
-        <v>25.72979970631166</v>
+        <v>23.9373178367716</v>
       </c>
       <c r="C905" t="n">
-        <v>49.91063129737348</v>
+        <v>48.43783682357099</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13335,10 +13335,10 @@
         <v>46308</v>
       </c>
       <c r="B1180" t="n">
-        <v>121</v>
+        <v>122.75</v>
       </c>
       <c r="C1180" t="n">
-        <v>207.6199951171875</v>
+        <v>209.6799926757812</v>
       </c>
     </row>
   </sheetData>
@@ -13377,10 +13377,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.4852342755657824</v>
+        <v>0.9540288650768503</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.9541074547215311</v>
+        <v>0.02862205895970416</v>
       </c>
     </row>
     <row r="3">
@@ -14049,10 +14049,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.4852342755657824</v>
+        <v>0.9540288650768503</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.9541074547215311</v>
+        <v>0.02862205895970416</v>
       </c>
     </row>
     <row r="3">
@@ -24239,10 +24239,10 @@
         <v>46308</v>
       </c>
       <c r="B905" t="n">
-        <v>23.9373178367716</v>
+        <v>25.72979970631166</v>
       </c>
       <c r="C905" t="n">
-        <v>48.43783682357099</v>
+        <v>49.91063129737348</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1180"/>
+  <dimension ref="A1:C1181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13332,13 +13332,24 @@
     </row>
     <row r="1180">
       <c r="A1180" s="2" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B1180" t="n">
-        <v>122.75</v>
+        <v>121.2399978637695</v>
       </c>
       <c r="C1180" t="n">
-        <v>209.6799926757812</v>
+        <v>208.6399993896484</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1181" t="n">
+        <v>119.7200012207031</v>
+      </c>
+      <c r="C1181" t="n">
+        <v>202.8000030517578</v>
       </c>
     </row>
   </sheetData>
@@ -13377,10 +13388,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9540288650768503</v>
+        <v>-1.537951454485542</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02862205895970416</v>
+        <v>-3.253502635384087</v>
       </c>
     </row>
     <row r="3">
@@ -14049,10 +14060,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9540288650768503</v>
+        <v>-1.537951454485542</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02862205895970416</v>
+        <v>-3.253502635384087</v>
       </c>
     </row>
     <row r="3">
@@ -14281,7 +14292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C905"/>
+  <dimension ref="A1:C906"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24236,13 +24247,24 @@
     </row>
     <row r="905">
       <c r="A905" s="2" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B905" t="n">
-        <v>25.72979970631166</v>
+        <v>24.18314173364886</v>
       </c>
       <c r="C905" t="n">
-        <v>49.91063129737348</v>
+        <v>49.16708849159767</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B906" t="n">
+        <v>23.33367837342912</v>
+      </c>
+      <c r="C906" t="n">
+        <v>45.10590370825929</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1181"/>
+  <dimension ref="A1:C1182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13343,13 +13343,24 @@
     </row>
     <row r="1181">
       <c r="A1181" s="2" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B1181" t="n">
-        <v>119.7200012207031</v>
+        <v>121</v>
       </c>
       <c r="C1181" t="n">
-        <v>202.8000030517578</v>
+        <v>207.6199951171875</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1182" t="n">
+        <v>119.8199996948242</v>
+      </c>
+      <c r="C1182" t="n">
+        <v>197.5700073242188</v>
       </c>
     </row>
   </sheetData>
@@ -13388,10 +13399,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.537951454485542</v>
+        <v>-1.455709101386682</v>
       </c>
       <c r="C2" t="n">
-        <v>-3.253502635384087</v>
+        <v>-5.748491591287486</v>
       </c>
     </row>
     <row r="3">
@@ -14060,10 +14071,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.537951454485542</v>
+        <v>-1.455709101386682</v>
       </c>
       <c r="C2" t="n">
-        <v>-3.253502635384087</v>
+        <v>-5.748491591287486</v>
       </c>
     </row>
     <row r="3">
@@ -14292,7 +14303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C906"/>
+  <dimension ref="A1:C907"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24258,13 +24269,24 @@
     </row>
     <row r="906">
       <c r="A906" s="2" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B906" t="n">
-        <v>23.33367837342912</v>
+        <v>24.65231315587584</v>
       </c>
       <c r="C906" t="n">
-        <v>45.10590370825929</v>
+        <v>48.55466748535997</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B907" t="n">
+        <v>20.76194136331326</v>
+      </c>
+      <c r="C907" t="n">
+        <v>37.51653778953279</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1182"/>
+  <dimension ref="A1:C1183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13354,13 +13354,24 @@
     </row>
     <row r="1182">
       <c r="A1182" s="2" t="n">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B1182" t="n">
-        <v>119.8199996948242</v>
+        <v>119.7200012207031</v>
       </c>
       <c r="C1182" t="n">
-        <v>197.5700073242188</v>
+        <v>202.8000030517578</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1183" t="n">
+        <v>120.1999969482422</v>
+      </c>
+      <c r="C1183" t="n">
+        <v>199.9400024414062</v>
       </c>
     </row>
   </sheetData>
@@ -13399,10 +13410,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.455709101386682</v>
+        <v>-1.143185649735301</v>
       </c>
       <c r="C2" t="n">
-        <v>-5.748491591287486</v>
+        <v>-4.617876586806369</v>
       </c>
     </row>
     <row r="3">
@@ -14071,10 +14082,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.455709101386682</v>
+        <v>-1.143185649735301</v>
       </c>
       <c r="C2" t="n">
-        <v>-5.748491591287486</v>
+        <v>-4.617876586806369</v>
       </c>
     </row>
     <row r="3">
@@ -14303,7 +14314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C907"/>
+  <dimension ref="A1:C908"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24280,13 +24291,24 @@
     </row>
     <row r="907">
       <c r="A907" s="2" t="n">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B907" t="n">
-        <v>20.76194136331326</v>
+        <v>20.6611567705993</v>
       </c>
       <c r="C907" t="n">
-        <v>37.51653778953279</v>
+        <v>41.15682163041443</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B908" t="n">
+        <v>20.610066758348</v>
+      </c>
+      <c r="C908" t="n">
+        <v>39.02099308802991</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1183"/>
+  <dimension ref="A1:C1184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13365,13 +13365,24 @@
     </row>
     <row r="1183">
       <c r="A1183" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1183" t="n">
+        <v>119.8199996948242</v>
+      </c>
+      <c r="C1183" t="n">
+        <v>197.5700073242188</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="2" t="n">
         <v>46311</v>
       </c>
-      <c r="B1183" t="n">
-        <v>120.1999969482422</v>
-      </c>
-      <c r="C1183" t="n">
-        <v>199.9400024414062</v>
+      <c r="B1184" t="n">
+        <v>119.8199996948242</v>
+      </c>
+      <c r="C1184" t="n">
+        <v>197.5700073242188</v>
       </c>
     </row>
   </sheetData>
@@ -13410,10 +13421,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.143185649735301</v>
+        <v>-1.455709101386682</v>
       </c>
       <c r="C2" t="n">
-        <v>-4.617876586806369</v>
+        <v>-5.748491591287486</v>
       </c>
     </row>
     <row r="3">
@@ -14082,10 +14093,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.143185649735301</v>
+        <v>-1.455709101386682</v>
       </c>
       <c r="C2" t="n">
-        <v>-4.617876586806369</v>
+        <v>-5.748491591287486</v>
       </c>
     </row>
     <row r="3">
@@ -14314,7 +14325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C908"/>
+  <dimension ref="A1:C909"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24302,13 +24313,24 @@
     </row>
     <row r="908">
       <c r="A908" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B908" t="n">
+        <v>20.22877312052482</v>
+      </c>
+      <c r="C908" t="n">
+        <v>37.37310336720356</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="2" t="n">
         <v>46311</v>
       </c>
-      <c r="B908" t="n">
-        <v>20.610066758348</v>
-      </c>
-      <c r="C908" t="n">
-        <v>39.02099308802991</v>
+      <c r="B909" t="n">
+        <v>17.82869192462107</v>
+      </c>
+      <c r="C909" t="n">
+        <v>30.90175373467803</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13379,10 +13379,10 @@
         <v>46311</v>
       </c>
       <c r="B1184" t="n">
-        <v>119.8199996948242</v>
+        <v>120.1999969482422</v>
       </c>
       <c r="C1184" t="n">
-        <v>197.5700073242188</v>
+        <v>199.9400024414062</v>
       </c>
     </row>
   </sheetData>
@@ -13421,10 +13421,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.455709101386682</v>
+        <v>-1.143185649735301</v>
       </c>
       <c r="C2" t="n">
-        <v>-5.748491591287486</v>
+        <v>-4.617876586806369</v>
       </c>
     </row>
     <row r="3">
@@ -14093,10 +14093,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.455709101386682</v>
+        <v>-1.143185649735301</v>
       </c>
       <c r="C2" t="n">
-        <v>-5.748491591287486</v>
+        <v>-4.617876586806369</v>
       </c>
     </row>
     <row r="3">
@@ -24327,10 +24327,10 @@
         <v>46311</v>
       </c>
       <c r="B909" t="n">
-        <v>17.82869192462107</v>
+        <v>18.20237394280857</v>
       </c>
       <c r="C909" t="n">
-        <v>30.90175373467803</v>
+        <v>32.47201493669012</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1184"/>
+  <dimension ref="A1:C1185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13383,6 +13383,17 @@
       </c>
       <c r="C1184" t="n">
         <v>199.9400024414062</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1185" t="n">
+        <v>119.8300018310547</v>
+      </c>
+      <c r="C1185" t="n">
+        <v>197.4400024414062</v>
       </c>
     </row>
   </sheetData>
@@ -13421,10 +13432,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.143185649735301</v>
+        <v>-1.447482983670001</v>
       </c>
       <c r="C2" t="n">
-        <v>-4.617876586806369</v>
+        <v>-5.810510905208288</v>
       </c>
     </row>
     <row r="3">
@@ -14093,10 +14104,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.143185649735301</v>
+        <v>-1.447482983670001</v>
       </c>
       <c r="C2" t="n">
-        <v>-4.617876586806369</v>
+        <v>-5.810510905208288</v>
       </c>
     </row>
     <row r="3">
@@ -14325,7 +14336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C909"/>
+  <dimension ref="A1:C910"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24331,6 +24342,17 @@
       </c>
       <c r="C909" t="n">
         <v>32.47201493669012</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B910" t="n">
+        <v>18.09401832017081</v>
+      </c>
+      <c r="C910" t="n">
+        <v>26.43442482789404</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13390,10 +13390,10 @@
         <v>46314</v>
       </c>
       <c r="B1185" t="n">
-        <v>119.8300018310547</v>
+        <v>120.1999969482422</v>
       </c>
       <c r="C1185" t="n">
-        <v>197.4400024414062</v>
+        <v>199.9400024414062</v>
       </c>
     </row>
   </sheetData>
@@ -13432,10 +13432,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.447482983670001</v>
+        <v>-1.143185649735301</v>
       </c>
       <c r="C2" t="n">
-        <v>-5.810510905208288</v>
+        <v>-4.617876586806369</v>
       </c>
     </row>
     <row r="3">
@@ -14104,10 +14104,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.447482983670001</v>
+        <v>-1.143185649735301</v>
       </c>
       <c r="C2" t="n">
-        <v>-5.810510905208288</v>
+        <v>-4.617876586806369</v>
       </c>
     </row>
     <row r="3">
@@ -24349,10 +24349,10 @@
         <v>46314</v>
       </c>
       <c r="B910" t="n">
-        <v>18.09401832017081</v>
+        <v>18.4586532987225</v>
       </c>
       <c r="C910" t="n">
-        <v>26.43442482789404</v>
+        <v>28.03534692149834</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13390,10 +13390,10 @@
         <v>46314</v>
       </c>
       <c r="B1185" t="n">
-        <v>120.1999969482422</v>
+        <v>119.8300018310547</v>
       </c>
       <c r="C1185" t="n">
-        <v>199.9400024414062</v>
+        <v>197.4400024414062</v>
       </c>
     </row>
   </sheetData>
@@ -13432,10 +13432,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.143185649735301</v>
+        <v>-1.447482983670001</v>
       </c>
       <c r="C2" t="n">
-        <v>-4.617876586806369</v>
+        <v>-5.810510905208288</v>
       </c>
     </row>
     <row r="3">
@@ -14104,10 +14104,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.143185649735301</v>
+        <v>-1.447482983670001</v>
       </c>
       <c r="C2" t="n">
-        <v>-4.617876586806369</v>
+        <v>-5.810510905208288</v>
       </c>
     </row>
     <row r="3">
@@ -24349,10 +24349,10 @@
         <v>46314</v>
       </c>
       <c r="B910" t="n">
-        <v>18.4586532987225</v>
+        <v>18.09401832017081</v>
       </c>
       <c r="C910" t="n">
-        <v>28.03534692149834</v>
+        <v>26.43442482789404</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1185"/>
+  <dimension ref="A1:C1186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13394,6 +13394,17 @@
       </c>
       <c r="C1185" t="n">
         <v>197.4400024414062</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1186" t="n">
+        <v>118.129997253418</v>
+      </c>
+      <c r="C1186" t="n">
+        <v>195.0599975585938</v>
       </c>
     </row>
   </sheetData>
@@ -13432,10 +13443,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.447482983670001</v>
+        <v>-2.845628085107876</v>
       </c>
       <c r="C2" t="n">
-        <v>-5.810510905208288</v>
+        <v>-6.94590110569081</v>
       </c>
     </row>
     <row r="3">
@@ -14104,10 +14115,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.447482983670001</v>
+        <v>-2.845628085107876</v>
       </c>
       <c r="C2" t="n">
-        <v>-5.810510905208288</v>
+        <v>-6.94590110569081</v>
       </c>
     </row>
     <row r="3">
@@ -14336,7 +14347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C910"/>
+  <dimension ref="A1:C911"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24353,6 +24364,17 @@
       </c>
       <c r="C910" t="n">
         <v>26.43442482789404</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B911" t="n">
+        <v>17.34379596905438</v>
+      </c>
+      <c r="C911" t="n">
+        <v>26.7281703995945</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1186"/>
+  <dimension ref="A1:C1187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13405,6 +13405,17 @@
       </c>
       <c r="C1186" t="n">
         <v>195.0599975585938</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1187" t="n">
+        <v>117.3499984741211</v>
+      </c>
+      <c r="C1187" t="n">
+        <v>189.9199981689453</v>
       </c>
     </row>
   </sheetData>
@@ -13443,10 +13454,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-2.845628085107876</v>
+        <v>-3.487127223844022</v>
       </c>
       <c r="C2" t="n">
-        <v>-6.94590110569081</v>
+        <v>-9.397956973154663</v>
       </c>
     </row>
     <row r="3">
@@ -14115,10 +14126,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-2.845628085107876</v>
+        <v>-3.487127223844022</v>
       </c>
       <c r="C2" t="n">
-        <v>-6.94590110569081</v>
+        <v>-9.397956973154663</v>
       </c>
     </row>
     <row r="3">
@@ -14347,7 +14358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C911"/>
+  <dimension ref="A1:C912"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24375,6 +24386,17 @@
       </c>
       <c r="C911" t="n">
         <v>26.7281703995945</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B912" t="n">
+        <v>14.32050338989639</v>
+      </c>
+      <c r="C912" t="n">
+        <v>15.56529292994568</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1187"/>
+  <dimension ref="A1:C1188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13416,6 +13416,17 @@
       </c>
       <c r="C1187" t="n">
         <v>189.9199981689453</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1188" t="n">
+        <v>115.9000015258789</v>
+      </c>
+      <c r="C1188" t="n">
+        <v>183.6699981689453</v>
       </c>
     </row>
   </sheetData>
@@ -13454,10 +13465,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-3.487127223844022</v>
+        <v>-4.679657030500762</v>
       </c>
       <c r="C2" t="n">
-        <v>-9.397956973154663</v>
+        <v>-12.37954276915946</v>
       </c>
     </row>
     <row r="3">
@@ -14126,10 +14137,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-3.487127223844022</v>
+        <v>-4.679657030500762</v>
       </c>
       <c r="C2" t="n">
-        <v>-9.397956973154663</v>
+        <v>-12.37954276915946</v>
       </c>
     </row>
     <row r="3">
@@ -14358,7 +14369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C912"/>
+  <dimension ref="A1:C913"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24397,6 +24408,17 @@
       </c>
       <c r="C912" t="n">
         <v>15.56529292994568</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B913" t="n">
+        <v>10.28642645797742</v>
+      </c>
+      <c r="C913" t="n">
+        <v>5.369743985685749</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13423,10 +13423,10 @@
         <v>46318</v>
       </c>
       <c r="B1188" t="n">
-        <v>115.9000015258789</v>
+        <v>117.3499984741211</v>
       </c>
       <c r="C1188" t="n">
-        <v>183.6699981689453</v>
+        <v>189.9199981689453</v>
       </c>
     </row>
   </sheetData>
@@ -13465,10 +13465,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.679657030500762</v>
+        <v>-3.487127223844022</v>
       </c>
       <c r="C2" t="n">
-        <v>-12.37954276915946</v>
+        <v>-9.397956973154663</v>
       </c>
     </row>
     <row r="3">
@@ -14137,10 +14137,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.679657030500762</v>
+        <v>-3.487127223844022</v>
       </c>
       <c r="C2" t="n">
-        <v>-12.37954276915946</v>
+        <v>-9.397956973154663</v>
       </c>
     </row>
     <row r="3">
@@ -24415,10 +24415,10 @@
         <v>46318</v>
       </c>
       <c r="B913" t="n">
-        <v>10.28642645797742</v>
+        <v>11.6661933233031</v>
       </c>
       <c r="C913" t="n">
-        <v>5.369743985685749</v>
+        <v>8.955309981634475</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13423,10 +13423,10 @@
         <v>46318</v>
       </c>
       <c r="B1188" t="n">
-        <v>117.3499984741211</v>
+        <v>115.9000015258789</v>
       </c>
       <c r="C1188" t="n">
-        <v>189.9199981689453</v>
+        <v>183.6699981689453</v>
       </c>
     </row>
   </sheetData>
@@ -13465,10 +13465,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-3.487127223844022</v>
+        <v>-4.679657030500762</v>
       </c>
       <c r="C2" t="n">
-        <v>-9.397956973154663</v>
+        <v>-12.37954276915946</v>
       </c>
     </row>
     <row r="3">
@@ -14137,10 +14137,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-3.487127223844022</v>
+        <v>-4.679657030500762</v>
       </c>
       <c r="C2" t="n">
-        <v>-9.397956973154663</v>
+        <v>-12.37954276915946</v>
       </c>
     </row>
     <row r="3">
@@ -24415,10 +24415,10 @@
         <v>46318</v>
       </c>
       <c r="B913" t="n">
-        <v>11.6661933233031</v>
+        <v>10.28642645797742</v>
       </c>
       <c r="C913" t="n">
-        <v>8.955309981634475</v>
+        <v>5.369743985685749</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1188"/>
+  <dimension ref="A1:C1189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13427,6 +13427,17 @@
       </c>
       <c r="C1188" t="n">
         <v>183.6699981689453</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1189" t="n">
+        <v>116.129997253418</v>
+      </c>
+      <c r="C1189" t="n">
+        <v>184.5099945068359</v>
       </c>
     </row>
   </sheetData>
@@ -13465,10 +13476,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.679657030500762</v>
+        <v>-4.490500245842332</v>
       </c>
       <c r="C2" t="n">
-        <v>-12.37954276915946</v>
+        <v>-11.97881938519934</v>
       </c>
     </row>
     <row r="3">
@@ -14137,10 +14148,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.679657030500762</v>
+        <v>-4.490500245842332</v>
       </c>
       <c r="C2" t="n">
-        <v>-12.37954276915946</v>
+        <v>-11.97881938519934</v>
       </c>
     </row>
     <row r="3">
@@ -14369,7 +14380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C913"/>
+  <dimension ref="A1:C914"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24419,6 +24430,17 @@
       </c>
       <c r="C913" t="n">
         <v>5.369743985685749</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B914" t="n">
+        <v>10.29537111181849</v>
+      </c>
+      <c r="C914" t="n">
+        <v>9.462504259172011</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13434,10 +13434,10 @@
         <v>46321</v>
       </c>
       <c r="B1189" t="n">
-        <v>116.129997253418</v>
+        <v>115.9000015258789</v>
       </c>
       <c r="C1189" t="n">
-        <v>184.5099945068359</v>
+        <v>183.6699981689453</v>
       </c>
     </row>
   </sheetData>
@@ -13476,10 +13476,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.490500245842332</v>
+        <v>-4.679657030500762</v>
       </c>
       <c r="C2" t="n">
-        <v>-11.97881938519934</v>
+        <v>-12.37954276915946</v>
       </c>
     </row>
     <row r="3">
@@ -14148,10 +14148,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.490500245842332</v>
+        <v>-4.679657030500762</v>
       </c>
       <c r="C2" t="n">
-        <v>-11.97881938519934</v>
+        <v>-12.37954276915946</v>
       </c>
     </row>
     <row r="3">
@@ -24437,10 +24437,10 @@
         <v>46321</v>
       </c>
       <c r="B914" t="n">
-        <v>10.29537111181849</v>
+        <v>10.07693087481669</v>
       </c>
       <c r="C914" t="n">
-        <v>9.462504259172011</v>
+        <v>8.964167554107316</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1189"/>
+  <dimension ref="A1:C1190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13434,10 +13434,21 @@
         <v>46321</v>
       </c>
       <c r="B1189" t="n">
-        <v>115.9000015258789</v>
+        <v>116.129997253418</v>
       </c>
       <c r="C1189" t="n">
-        <v>183.6699981689453</v>
+        <v>184.5099945068359</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1190" t="n">
+        <v>115.6399993896484</v>
+      </c>
+      <c r="C1190" t="n">
+        <v>181.4299926757812</v>
       </c>
     </row>
   </sheetData>
@@ -13476,10 +13487,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.679657030500762</v>
+        <v>-4.893492168309255</v>
       </c>
       <c r="C2" t="n">
-        <v>-12.37954276915946</v>
+        <v>-13.44814573898196</v>
       </c>
     </row>
     <row r="3">
@@ -14148,10 +14159,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.679657030500762</v>
+        <v>-4.893492168309255</v>
       </c>
       <c r="C2" t="n">
-        <v>-12.37954276915946</v>
+        <v>-13.44814573898196</v>
       </c>
     </row>
     <row r="3">
@@ -14380,7 +14391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C914"/>
+  <dimension ref="A1:C915"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24437,10 +24448,21 @@
         <v>46321</v>
       </c>
       <c r="B914" t="n">
-        <v>10.07693087481669</v>
+        <v>10.29537111181849</v>
       </c>
       <c r="C914" t="n">
-        <v>8.964167554107316</v>
+        <v>9.462504259172011</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B915" t="n">
+        <v>9.74660375378944</v>
+      </c>
+      <c r="C915" t="n">
+        <v>15.40613505983501</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13445,10 +13445,10 @@
         <v>46322</v>
       </c>
       <c r="B1190" t="n">
-        <v>115.6399993896484</v>
+        <v>116.129997253418</v>
       </c>
       <c r="C1190" t="n">
-        <v>181.4299926757812</v>
+        <v>184.5099945068359</v>
       </c>
     </row>
   </sheetData>
@@ -13487,10 +13487,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.893492168309255</v>
+        <v>-4.490500245842332</v>
       </c>
       <c r="C2" t="n">
-        <v>-13.44814573898196</v>
+        <v>-11.97881938519934</v>
       </c>
     </row>
     <row r="3">
@@ -14159,10 +14159,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.893492168309255</v>
+        <v>-4.490500245842332</v>
       </c>
       <c r="C2" t="n">
-        <v>-13.44814573898196</v>
+        <v>-11.97881938519934</v>
       </c>
     </row>
     <row r="3">
@@ -24459,10 +24459,10 @@
         <v>46322</v>
       </c>
       <c r="B915" t="n">
-        <v>9.74660375378944</v>
+        <v>10.21162971089034</v>
       </c>
       <c r="C915" t="n">
-        <v>15.40613505983501</v>
+        <v>17.36529904400841</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1190"/>
+  <dimension ref="A1:C1191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13445,10 +13445,21 @@
         <v>46322</v>
       </c>
       <c r="B1190" t="n">
-        <v>116.129997253418</v>
+        <v>115.6399993896484</v>
       </c>
       <c r="C1190" t="n">
-        <v>184.5099945068359</v>
+        <v>181.4299926757812</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1191" t="n">
+        <v>117.129997253418</v>
+      </c>
+      <c r="C1191" t="n">
+        <v>183.6100006103516</v>
       </c>
     </row>
   </sheetData>
@@ -13487,10 +13498,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.490500245842332</v>
+        <v>-3.668064165475104</v>
       </c>
       <c r="C2" t="n">
-        <v>-11.97881938519934</v>
+        <v>-12.40816482811915</v>
       </c>
     </row>
     <row r="3">
@@ -14159,10 +14170,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.490500245842332</v>
+        <v>-3.668064165475104</v>
       </c>
       <c r="C2" t="n">
-        <v>-11.97881938519934</v>
+        <v>-12.40816482811915</v>
       </c>
     </row>
     <row r="3">
@@ -14391,7 +14402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C915"/>
+  <dimension ref="A1:C916"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24459,10 +24470,21 @@
         <v>46322</v>
       </c>
       <c r="B915" t="n">
-        <v>10.21162971089034</v>
+        <v>9.74660375378944</v>
       </c>
       <c r="C915" t="n">
-        <v>17.36529904400841</v>
+        <v>15.40613505983501</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B916" t="n">
+        <v>8.343350839092256</v>
+      </c>
+      <c r="C916" t="n">
+        <v>14.32751782836466</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13456,10 +13456,10 @@
         <v>46323</v>
       </c>
       <c r="B1191" t="n">
-        <v>117.129997253418</v>
+        <v>115.6399993896484</v>
       </c>
       <c r="C1191" t="n">
-        <v>183.6100006103516</v>
+        <v>181.4299926757812</v>
       </c>
     </row>
   </sheetData>
@@ -13498,10 +13498,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-3.668064165475104</v>
+        <v>-4.893492168309255</v>
       </c>
       <c r="C2" t="n">
-        <v>-12.40816482811915</v>
+        <v>-13.44814573898196</v>
       </c>
     </row>
     <row r="3">
@@ -14170,10 +14170,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-3.668064165475104</v>
+        <v>-4.893492168309255</v>
       </c>
       <c r="C2" t="n">
-        <v>-12.40816482811915</v>
+        <v>-13.44814573898196</v>
       </c>
     </row>
     <row r="3">
@@ -24481,10 +24481,10 @@
         <v>46323</v>
       </c>
       <c r="B916" t="n">
-        <v>8.343350839092256</v>
+        <v>6.965126941804756</v>
       </c>
       <c r="C916" t="n">
-        <v>14.32751782836466</v>
+        <v>12.9701032257991</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1191"/>
+  <dimension ref="A1:C1192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13456,10 +13456,21 @@
         <v>46323</v>
       </c>
       <c r="B1191" t="n">
-        <v>115.6399993896484</v>
+        <v>117.129997253418</v>
       </c>
       <c r="C1191" t="n">
-        <v>181.4299926757812</v>
+        <v>183.6100006103516</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="2" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1192" t="n">
+        <v>116.370002746582</v>
+      </c>
+      <c r="C1192" t="n">
+        <v>179.8099975585938</v>
       </c>
     </row>
   </sheetData>
@@ -13498,10 +13509,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.893492168309255</v>
+        <v>-4.293111068777877</v>
       </c>
       <c r="C2" t="n">
-        <v>-13.44814573898196</v>
+        <v>-14.22097044794251</v>
       </c>
     </row>
     <row r="3">
@@ -14170,10 +14181,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.893492168309255</v>
+        <v>-4.293111068777877</v>
       </c>
       <c r="C2" t="n">
-        <v>-13.44814573898196</v>
+        <v>-14.22097044794251</v>
       </c>
     </row>
     <row r="3">
@@ -14402,7 +14413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C916"/>
+  <dimension ref="A1:C917"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24481,10 +24492,21 @@
         <v>46323</v>
       </c>
       <c r="B916" t="n">
-        <v>6.965126941804756</v>
+        <v>8.343350839092256</v>
       </c>
       <c r="C916" t="n">
-        <v>12.9701032257991</v>
+        <v>14.32751782836466</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="2" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B917" t="n">
+        <v>10.6810000210436</v>
+      </c>
+      <c r="C917" t="n">
+        <v>20.82380641660655</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13467,10 +13467,10 @@
         <v>46324</v>
       </c>
       <c r="B1192" t="n">
-        <v>116.370002746582</v>
+        <v>117.129997253418</v>
       </c>
       <c r="C1192" t="n">
-        <v>179.8099975585938</v>
+        <v>183.6100006103516</v>
       </c>
     </row>
   </sheetData>
@@ -13509,10 +13509,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.293111068777877</v>
+        <v>-3.668064165475104</v>
       </c>
       <c r="C2" t="n">
-        <v>-14.22097044794251</v>
+        <v>-12.40816482811915</v>
       </c>
     </row>
     <row r="3">
@@ -14181,10 +14181,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.293111068777877</v>
+        <v>-3.668064165475104</v>
       </c>
       <c r="C2" t="n">
-        <v>-14.22097044794251</v>
+        <v>-12.40816482811915</v>
       </c>
     </row>
     <row r="3">
@@ -24503,10 +24503,10 @@
         <v>46324</v>
       </c>
       <c r="B917" t="n">
-        <v>10.6810000210436</v>
+        <v>11.40384053012464</v>
       </c>
       <c r="C917" t="n">
-        <v>20.82380641660655</v>
+        <v>23.37722858079119</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1192"/>
+  <dimension ref="A1:C1193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13467,10 +13467,21 @@
         <v>46324</v>
       </c>
       <c r="B1192" t="n">
-        <v>117.129997253418</v>
+        <v>116.370002746582</v>
       </c>
       <c r="C1192" t="n">
-        <v>183.6100006103516</v>
+        <v>179.8099975585938</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="2" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1193" t="n">
+        <v>115.2300033569336</v>
+      </c>
+      <c r="C1193" t="n">
+        <v>173.3399963378906</v>
       </c>
     </row>
   </sheetData>
@@ -13509,10 +13520,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-3.668064165475104</v>
+        <v>-5.230687698421366</v>
       </c>
       <c r="C2" t="n">
-        <v>-12.40816482811915</v>
+        <v>-17.30750864630764</v>
       </c>
     </row>
     <row r="3">
@@ -14181,10 +14192,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-3.668064165475104</v>
+        <v>-5.230687698421366</v>
       </c>
       <c r="C2" t="n">
-        <v>-12.40816482811915</v>
+        <v>-17.30750864630764</v>
       </c>
     </row>
     <row r="3">
@@ -14413,7 +14424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C917"/>
+  <dimension ref="A1:C918"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24503,10 +24514,21 @@
         <v>46324</v>
       </c>
       <c r="B917" t="n">
-        <v>11.40384053012464</v>
+        <v>10.6810000210436</v>
       </c>
       <c r="C917" t="n">
-        <v>23.37722858079119</v>
+        <v>20.82380641660655</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="2" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B918" t="n">
+        <v>9.026398614018616</v>
+      </c>
+      <c r="C918" t="n">
+        <v>19.29799910337551</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13478,10 +13478,10 @@
         <v>46325</v>
       </c>
       <c r="B1193" t="n">
-        <v>115.2300033569336</v>
+        <v>116.370002746582</v>
       </c>
       <c r="C1193" t="n">
-        <v>173.3399963378906</v>
+        <v>179.8099975585938</v>
       </c>
     </row>
   </sheetData>
@@ -13520,10 +13520,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-5.230687698421366</v>
+        <v>-4.293111068777877</v>
       </c>
       <c r="C2" t="n">
-        <v>-17.30750864630764</v>
+        <v>-14.22097044794251</v>
       </c>
     </row>
     <row r="3">
@@ -14192,10 +14192,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-5.230687698421366</v>
+        <v>-4.293111068777877</v>
       </c>
       <c r="C2" t="n">
-        <v>-17.30750864630764</v>
+        <v>-14.22097044794251</v>
       </c>
     </row>
     <row r="3">
@@ -24525,10 +24525,10 @@
         <v>46325</v>
       </c>
       <c r="B918" t="n">
-        <v>9.026398614018616</v>
+        <v>10.10502418248755</v>
       </c>
       <c r="C918" t="n">
-        <v>19.29799910337551</v>
+        <v>23.75085600964717</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Gold & Silver.xlsx
+++ b/dashboards/Gold & Silver.xlsx
@@ -13478,10 +13478,10 @@
         <v>46325</v>
       </c>
       <c r="B1193" t="n">
-        <v>116.370002746582</v>
+        <v>115.2300033569336</v>
       </c>
       <c r="C1193" t="n">
-        <v>179.8099975585938</v>
+        <v>173.3399963378906</v>
       </c>
     </row>
   </sheetData>
@@ -13520,10 +13520,10 @@
         <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.293111068777877</v>
+        <v>-5.230687698421366</v>
       </c>
       <c r="C2" t="n">
-        <v>-14.22097044794251</v>
+        <v>-17.30750864630764</v>
       </c>
     </row>
     <row r="3">
@@ -14192,10 +14192,10 @@
         <v>46387</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.293111068777877</v>
+        <v>-5.230687698421366</v>
       </c>
       <c r="C2" t="n">
-        <v>-14.22097044794251</v>
+        <v>-17.30750864630764</v>
       </c>
     </row>
     <row r="3">
@@ -24525,10 +24525,10 @@
         <v>46325</v>
       </c>
       <c r="B918" t="n">
-        <v>10.10502418248755</v>
+        <v>9.026398614018616</v>
       </c>
       <c r="C918" t="n">
-        <v>23.75085600964717</v>
+        <v>19.29799910337551</v>
       </c>
     </row>
   </sheetData>
